--- a/Thread_Certified_Products_All.xlsx
+++ b/Thread_Certified_Products_All.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Charts &amp; Analysis" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Products'!$A$4:$G$488</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Products'!$A$4:$G$496</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Company Summary'!$A$3:$E$140</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1020,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G488"/>
+  <dimension ref="A1:G496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1042,7 +1042,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: threadgroup.org/Certified-Products  |  Total: 484 products  |  Updated: 2026-09-28</t>
+          <t>Source: threadgroup.org/Certified-Products  |  Total: 492 products  |  Updated: 2026-10-28</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>BILRESA scroll wheel</t>
+          <t>BILRESA dual button (E2622)</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>DUBBELKISEL</t>
+          <t>BILRESA scroll wheel</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>GRILLPLATS plug</t>
+          <t>BILRESA scroll wheel (E2704)</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr"/>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>KAJPLATS E12 CWS globe 800lm</t>
+          <t>DUBBELKISEL</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr"/>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>KAJPLATS E14 CWS globe 806lm</t>
+          <t>GRILLPLATS plug</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>Smart plug</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>KAJPLATS E26 CWS globe 1100lm</t>
+          <t>KAJPLATS E12 CWS globe 800lm</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>KAJPLATS E27 CWS globe 1055lm</t>
+          <t>KAJPLATS E14 CWS globe 806lm</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="C166" s="7" t="inlineStr">
         <is>
-          <t>KAJPLATS GU10 CWS 575lm</t>
+          <t>KAJPLATS E26 CWS globe 1100lm</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>KAJPLATS GU10 CWS 575lm</t>
+          <t>KAJPLATS E27 CWS globe 1055lm</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>KAJPLATS WS</t>
+          <t>KAJPLATS GU10 CWS 575lm</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Bulb, Light</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr"/>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>KAJPLATS WS</t>
+          <t>KAJPLATS GU10 CWS 575lm</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Bulb, Light</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>KLIPPBOK water leak sensor</t>
+          <t>KAJPLATS WS</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Bulb, Light</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr"/>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>MYGGBETT door/window sensor (E2492)</t>
+          <t>KAJPLATS WS</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Bulb, Light</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr"/>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>MYGGSPRAY wrlss mtn sensor (E2494)</t>
+          <t>KLIPPBOK water leak sensor</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G172" s="7" t="inlineStr"/>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>TIMMERFLOTTE temp/hmd sensor</t>
+          <t>MYGGBETT door/window sensor (E2492)</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr"/>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="C174" s="7" t="inlineStr">
         <is>
-          <t>TOFSMYGGA plug</t>
+          <t>MYGGBETT door/window sensor (E2705)</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
@@ -6344,12 +6344,12 @@
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G174" s="7" t="inlineStr"/>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>TOFSMYGGA plug outdoor</t>
+          <t>MYGGSPRAY wrlss mtn sensor (E2494)</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr"/>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>VARMBLIXT table/wall lamp</t>
+          <t>MYGGSPRAY wrlss mtn sensor (E2706)</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr"/>
@@ -10514,27 +10514,27 @@
       </c>
       <c r="B309" s="5" t="inlineStr">
         <is>
-          <t>Qingdao Heffeix Technology Co., Ltd</t>
+          <t>PIN Genie Inc, DBA Lockly</t>
         </is>
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>Heffeix-BR</t>
+          <t>Lockly Styla Visage Mortise Edition</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E309" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr"/>
@@ -10545,27 +10545,27 @@
       </c>
       <c r="B310" s="7" t="inlineStr">
         <is>
-          <t>Qingdao Yeelink Information Technology Co., Ltd</t>
+          <t>Qingdao Heffeix Technology Co., Ltd</t>
         </is>
       </c>
       <c r="C310" s="7" t="inlineStr">
         <is>
-          <t>Smart Switch</t>
+          <t>Heffeix-BR</t>
         </is>
       </c>
       <c r="D310" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E310" s="6" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G310" s="7" t="inlineStr"/>
@@ -10581,22 +10581,22 @@
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>Yeelight Pro Smart Home Hub</t>
+          <t>Smart Switch</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E311" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr"/>
@@ -10612,22 +10612,22 @@
       </c>
       <c r="C312" s="7" t="inlineStr">
         <is>
-          <t>Yeelight Pro Torkey Smart RGBCW LED bulb</t>
+          <t>Yeelight Pro Smart Home Hub</t>
         </is>
       </c>
       <c r="D312" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E312" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G312" s="7" t="inlineStr"/>
@@ -10643,7 +10643,7 @@
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>Yeelight RGBlC Smart LED Neon Rope Light</t>
+          <t>Yeelight Pro Torkey Smart RGBCW LED bulb</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>Lightstrip</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C314" s="7" t="inlineStr">
         <is>
-          <t>Yeelight Smart Bath Heater D1</t>
+          <t>Yeelight RGBlC Smart LED Neon Rope Light</t>
         </is>
       </c>
       <c r="D314" s="6" t="inlineStr">
@@ -10684,12 +10684,12 @@
       </c>
       <c r="E314" s="6" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lightstrip</t>
         </is>
       </c>
       <c r="G314" s="7" t="inlineStr"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>Yeelight Smart Ceiling Fan-Light S1</t>
+          <t>Yeelight Smart Bath Heater D1</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -10715,12 +10715,12 @@
       </c>
       <c r="E315" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr"/>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="C316" s="7" t="inlineStr">
         <is>
-          <t>Yeelight Smart Ceiling Light 320</t>
+          <t>Yeelight Smart Ceiling Fan-Light S1</t>
         </is>
       </c>
       <c r="D316" s="6" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>Yeelight Smart Ceiling Light 450</t>
+          <t>Yeelight Smart Ceiling Light 320</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="C318" s="7" t="inlineStr">
         <is>
-          <t>Yeelight Smart LED Bedside Lamp D1</t>
+          <t>Yeelight Smart Ceiling Light 450</t>
         </is>
       </c>
       <c r="D318" s="6" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>Yeelight Smart LED Desk Lamp D1</t>
+          <t>Yeelight Smart LED Bedside Lamp D1</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -10855,27 +10855,27 @@
       </c>
       <c r="B320" s="7" t="inlineStr">
         <is>
-          <t>Qorvo Utrecht B.V.</t>
+          <t>Qingdao Yeelink Information Technology Co., Ltd</t>
         </is>
       </c>
       <c r="C320" s="7" t="inlineStr">
         <is>
-          <t>GP712</t>
+          <t>Yeelight Smart LED Desk Lamp D1</t>
         </is>
       </c>
       <c r="D320" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E320" s="6" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G320" s="7" t="inlineStr"/>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>QPG6105</t>
+          <t>GP712</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="C322" s="7" t="inlineStr">
         <is>
-          <t>QPG6200</t>
+          <t>QPG6105</t>
         </is>
       </c>
       <c r="D322" s="6" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>QPG7015M</t>
+          <t>QPG6200</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="B324" s="7" t="inlineStr">
         <is>
-          <t>Qualcomm Inc.</t>
+          <t>Qorvo Utrecht B.V.</t>
         </is>
       </c>
       <c r="C324" s="7" t="inlineStr">
         <is>
-          <t>QCA 4020</t>
+          <t>QPG7015M</t>
         </is>
       </c>
       <c r="D324" s="6" t="inlineStr">
@@ -11010,12 +11010,12 @@
       </c>
       <c r="B325" s="5" t="inlineStr">
         <is>
-          <t>Quectel Wireless Solutions Co., Ltd.</t>
+          <t>Qualcomm Inc.</t>
         </is>
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>KGM133S</t>
+          <t>QCA 4020</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="E325" s="4" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="B326" s="7" t="inlineStr">
         <is>
-          <t>Rafael Microelectronics, Inc.</t>
+          <t>Quectel Wireless Solutions Co., Ltd.</t>
         </is>
       </c>
       <c r="C326" s="7" t="inlineStr">
         <is>
-          <t>2.4G Wireless SOC E2</t>
+          <t>KGM133S</t>
         </is>
       </c>
       <c r="D326" s="6" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="E326" s="6" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F326" s="6" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="C327" s="5" t="inlineStr">
         <is>
-          <t>RT582 + OpenThread SDK (V1.3.0)</t>
+          <t>2.4G Wireless SOC E2</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="C328" s="7" t="inlineStr">
         <is>
-          <t>RT583</t>
+          <t>RT582 + OpenThread SDK (V1.3.0)</t>
         </is>
       </c>
       <c r="D328" s="6" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="C329" s="5" t="inlineStr">
         <is>
-          <t>Rafael RT584x</t>
+          <t>RT583</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -11170,22 +11170,22 @@
       </c>
       <c r="C330" s="7" t="inlineStr">
         <is>
-          <t>Smart Wall Switch</t>
+          <t>Rafael RT584x</t>
         </is>
       </c>
       <c r="D330" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E330" s="6" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G330" s="7" t="inlineStr"/>
@@ -11196,27 +11196,27 @@
       </c>
       <c r="B331" s="5" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Rafael Microelectronics, Inc.</t>
         </is>
       </c>
       <c r="C331" s="5" t="inlineStr">
         <is>
-          <t>OT Border Router with Realtek AmebaSmart and RTL877x RCP</t>
+          <t>Smart Wall Switch</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G331" s="5" t="inlineStr"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="C332" s="7" t="inlineStr">
         <is>
-          <t>RTL877x series SoC</t>
+          <t>OT Border Router with Realtek AmebaSmart and RTL877x RCP</t>
         </is>
       </c>
       <c r="D332" s="6" t="inlineStr">
@@ -11242,7 +11242,7 @@
       </c>
       <c r="E332" s="6" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F332" s="6" t="inlineStr">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="C333" s="5" t="inlineStr">
         <is>
-          <t>Realtek Wi-Fi+BT+802.15.4 3-in-1 NIC Combo SoC</t>
+          <t>RTL877x series SoC</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
@@ -11289,27 +11289,27 @@
       </c>
       <c r="B334" s="7" t="inlineStr">
         <is>
-          <t>Robert Bosch GmbH</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="C334" s="7" t="inlineStr">
         <is>
-          <t>Door-/Window Contact II [+M]</t>
+          <t>Realtek Wi-Fi+BT+802.15.4 3-in-1 NIC Combo SoC</t>
         </is>
       </c>
       <c r="D334" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E334" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G334" s="7" t="inlineStr"/>
@@ -11325,7 +11325,7 @@
       </c>
       <c r="C335" s="5" t="inlineStr">
         <is>
-          <t>Motion Detector II [+M]</t>
+          <t>Door-/Window Contact II [+M]</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G335" s="5" t="inlineStr"/>
@@ -11356,7 +11356,7 @@
       </c>
       <c r="C336" s="7" t="inlineStr">
         <is>
-          <t>Plug Compact [+M]</t>
+          <t>Motion Detector II [+M]</t>
         </is>
       </c>
       <c r="D336" s="6" t="inlineStr">
@@ -11366,12 +11366,12 @@
       </c>
       <c r="E336" s="6" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G336" s="7" t="inlineStr"/>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="C337" s="5" t="inlineStr">
         <is>
-          <t>Radiator Thermostat II [+M]</t>
+          <t>Plug Compact [+M]</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="E337" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>Smart plug</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr"/>
@@ -11413,12 +11413,12 @@
       </c>
       <c r="B338" s="7" t="inlineStr">
         <is>
-          <t>SENSEREO LIMITED</t>
+          <t>Robert Bosch GmbH</t>
         </is>
       </c>
       <c r="C338" s="7" t="inlineStr">
         <is>
-          <t>Sensereo Matter Smoke Alarm</t>
+          <t>Radiator Thermostat II [+M]</t>
         </is>
       </c>
       <c r="D338" s="6" t="inlineStr">
@@ -11428,12 +11428,12 @@
       </c>
       <c r="E338" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>Smoke alarm</t>
+          <t>Heating</t>
         </is>
       </c>
       <c r="G338" s="7" t="inlineStr"/>
@@ -11444,12 +11444,12 @@
       </c>
       <c r="B339" s="5" t="inlineStr">
         <is>
-          <t>SHENZHEN DEASINO TECHNOLOGY CO.,LTD</t>
+          <t>SENSEREO LIMITED</t>
         </is>
       </c>
       <c r="C339" s="5" t="inlineStr">
         <is>
-          <t>Matter LOCK</t>
+          <t>Sensereo Matter Smoke Alarm</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Smoke alarm</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr"/>
@@ -11480,22 +11480,22 @@
       </c>
       <c r="C340" s="7" t="inlineStr">
         <is>
-          <t>Matter module</t>
+          <t>Matter LOCK</t>
         </is>
       </c>
       <c r="D340" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E340" s="6" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G340" s="7" t="inlineStr"/>
@@ -11506,27 +11506,27 @@
       </c>
       <c r="B341" s="5" t="inlineStr">
         <is>
-          <t>SIEGENIA-AUBI KG</t>
+          <t>SHENZHEN DEASINO TECHNOLOGY CO.,LTD</t>
         </is>
       </c>
       <c r="C341" s="5" t="inlineStr">
         <is>
-          <t>Smart Sensor</t>
+          <t>Matter module</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E341" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G341" s="5" t="inlineStr"/>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="C342" s="7" t="inlineStr">
         <is>
-          <t>Smart Window Handle</t>
+          <t>Smart Sensor</t>
         </is>
       </c>
       <c r="D342" s="6" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="E342" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>Window lock</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G342" s="7" t="inlineStr"/>
@@ -11568,27 +11568,27 @@
       </c>
       <c r="B343" s="5" t="inlineStr">
         <is>
-          <t>STMicroelectronics International N.V.</t>
+          <t>SIEGENIA-AUBI KG</t>
         </is>
       </c>
       <c r="C343" s="5" t="inlineStr">
         <is>
-          <t>STM32WB</t>
+          <t>Smart Window Handle</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E343" s="4" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Window lock</t>
         </is>
       </c>
       <c r="G343" s="5" t="inlineStr"/>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="C344" s="7" t="inlineStr">
         <is>
-          <t>STM32WB (Nucleo)</t>
+          <t>STM32WB</t>
         </is>
       </c>
       <c r="D344" s="6" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="E344" s="6" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F344" s="6" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="C345" s="5" t="inlineStr">
         <is>
-          <t>STM32WBA</t>
+          <t>STM32WB (Nucleo)</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="C346" s="7" t="inlineStr">
         <is>
-          <t>STM32WBA65I-DK1 Discovery kit</t>
+          <t>STM32WB5MMG</t>
         </is>
       </c>
       <c r="D346" s="6" t="inlineStr">
@@ -11692,12 +11692,12 @@
       </c>
       <c r="B347" s="5" t="inlineStr">
         <is>
-          <t>Samsung SmartThings</t>
+          <t>STMicroelectronics International N.V.</t>
         </is>
       </c>
       <c r="C347" s="5" t="inlineStr">
         <is>
-          <t>Harman Kardon Virtuo</t>
+          <t>STM32WBA</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="E347" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>Smart speaker</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G347" s="5" t="inlineStr"/>
@@ -11723,12 +11723,12 @@
       </c>
       <c r="B348" s="7" t="inlineStr">
         <is>
-          <t>Samsung SmartThings</t>
+          <t>STMicroelectronics International N.V.</t>
         </is>
       </c>
       <c r="C348" s="7" t="inlineStr">
         <is>
-          <t>R95H</t>
+          <t>STM32WBA65I-DK1 Discovery kit</t>
         </is>
       </c>
       <c r="D348" s="6" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="E348" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F348" s="6" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="C349" s="5" t="inlineStr">
         <is>
-          <t>S95H</t>
+          <t>Harman Kardon Virtuo</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E349" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Smart speaker</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr"/>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="C350" s="7" t="inlineStr">
         <is>
-          <t>Samsung Monitor</t>
+          <t>R95H</t>
         </is>
       </c>
       <c r="D350" s="6" t="inlineStr">
@@ -11800,12 +11800,12 @@
       </c>
       <c r="E350" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G350" s="7" t="inlineStr"/>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="C351" s="5" t="inlineStr">
         <is>
-          <t>Samsung Signage</t>
+          <t>S95H</t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="E351" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr"/>
@@ -11852,7 +11852,7 @@
       </c>
       <c r="C352" s="7" t="inlineStr">
         <is>
-          <t>Samsung Smart TV</t>
+          <t>Samsung Monitor</t>
         </is>
       </c>
       <c r="D352" s="6" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="C353" s="5" t="inlineStr">
         <is>
-          <t>Samsung SmartThings Hub V3</t>
+          <t>Samsung Signage</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="E353" s="4" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="C354" s="7" t="inlineStr">
         <is>
-          <t>Samsung SmartThings Station</t>
+          <t>Samsung Smart TV</t>
         </is>
       </c>
       <c r="D354" s="6" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="C355" s="5" t="inlineStr">
         <is>
-          <t>Samsung Soundbar</t>
+          <t>Samsung SmartThings Hub V3</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="E355" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="C356" s="7" t="inlineStr">
         <is>
-          <t>SmartThings Hub V3</t>
+          <t>Samsung SmartThings Station</t>
         </is>
       </c>
       <c r="D356" s="6" t="inlineStr">
@@ -12002,27 +12002,27 @@
       </c>
       <c r="B357" s="5" t="inlineStr">
         <is>
-          <t>Savant</t>
+          <t>Samsung SmartThings</t>
         </is>
       </c>
       <c r="C357" s="5" t="inlineStr">
         <is>
-          <t>Smart window covering</t>
+          <t>Samsung Soundbar</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E357" s="4" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G357" s="5" t="inlineStr"/>
@@ -12033,27 +12033,27 @@
       </c>
       <c r="B358" s="7" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Samsung SmartThings</t>
         </is>
       </c>
       <c r="C358" s="7" t="inlineStr">
         <is>
-          <t>Funktaster Connected</t>
+          <t>SmartThings Hub V3</t>
         </is>
       </c>
       <c r="D358" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E358" s="6" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G358" s="7" t="inlineStr"/>
@@ -12064,12 +12064,12 @@
       </c>
       <c r="B359" s="5" t="inlineStr">
         <is>
-          <t>Schüco Polymer Technologies KG</t>
+          <t>Savant</t>
         </is>
       </c>
       <c r="C359" s="5" t="inlineStr">
         <is>
-          <t>Schüco Funksensor</t>
+          <t>Smart window covering</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="E359" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Curtain</t>
         </is>
       </c>
       <c r="G359" s="5" t="inlineStr"/>
@@ -12095,12 +12095,12 @@
       </c>
       <c r="B360" s="7" t="inlineStr">
         <is>
-          <t>Secuyou</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C360" s="7" t="inlineStr">
         <is>
-          <t>Secuyou Smart Lock</t>
+          <t>Energy Data Processor Wireless</t>
         </is>
       </c>
       <c r="D360" s="6" t="inlineStr">
@@ -12110,12 +12110,12 @@
       </c>
       <c r="E360" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G360" s="7" t="inlineStr"/>
@@ -12126,27 +12126,27 @@
       </c>
       <c r="B361" s="5" t="inlineStr">
         <is>
-          <t>Sercomm Corporation</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C361" s="5" t="inlineStr">
         <is>
-          <t>SAX2V1R</t>
+          <t>Funktaster Connected</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E361" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>Wi-Fi Access Point</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G361" s="5" t="inlineStr"/>
@@ -12157,27 +12157,27 @@
       </c>
       <c r="B362" s="7" t="inlineStr">
         <is>
-          <t>Sercomm Corporation</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C362" s="7" t="inlineStr">
         <is>
-          <t>SBE1V1R</t>
+          <t>Temperature/Humidity Sensor</t>
         </is>
       </c>
       <c r="D362" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E362" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>Wi-Fi Access Point</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G362" s="7" t="inlineStr"/>
@@ -12188,27 +12188,27 @@
       </c>
       <c r="B363" s="5" t="inlineStr">
         <is>
-          <t>Shanghai Poyu Intelligent Technology Co., Ltd.</t>
+          <t>Schüco Polymer Technologies KG</t>
         </is>
       </c>
       <c r="C363" s="5" t="inlineStr">
         <is>
-          <t>Morelinks Thread Module (TN54AE)</t>
+          <t>Schüco Funksensor</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G363" s="5" t="inlineStr"/>
@@ -12219,27 +12219,27 @@
       </c>
       <c r="B364" s="7" t="inlineStr">
         <is>
-          <t>Shanghai Poyu Intelligent Technology Co., Ltd.</t>
+          <t>Secuyou</t>
         </is>
       </c>
       <c r="C364" s="7" t="inlineStr">
         <is>
-          <t>Morelinks Thread Module (TN54BE)</t>
+          <t>Secuyou Smart Lock</t>
         </is>
       </c>
       <c r="D364" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E364" s="6" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G364" s="7" t="inlineStr"/>
@@ -12250,27 +12250,27 @@
       </c>
       <c r="B365" s="5" t="inlineStr">
         <is>
-          <t>Shenzhen Haojai Lianchuang Technology Co.,Ltd</t>
+          <t>Sercomm Corporation</t>
         </is>
       </c>
       <c r="C365" s="5" t="inlineStr">
         <is>
-          <t>HAOJAI Smart Switch</t>
+          <t>SAX2V1R</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E365" s="4" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Wi-Fi Access Point</t>
         </is>
       </c>
       <c r="G365" s="5" t="inlineStr"/>
@@ -12281,27 +12281,27 @@
       </c>
       <c r="B366" s="7" t="inlineStr">
         <is>
-          <t>Shenzhen Haojai Lianchuang Technology Co.,Ltd</t>
+          <t>Sercomm Corporation</t>
         </is>
       </c>
       <c r="C366" s="7" t="inlineStr">
         <is>
-          <t>Smart Curtain</t>
+          <t>SBE1V1R</t>
         </is>
       </c>
       <c r="D366" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E366" s="6" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Wi-Fi Access Point</t>
         </is>
       </c>
       <c r="G366" s="7" t="inlineStr"/>
@@ -12312,27 +12312,27 @@
       </c>
       <c r="B367" s="5" t="inlineStr">
         <is>
-          <t>Shenzhen Heiman Technology Co., Ltd.</t>
+          <t>Shanghai Poyu Intelligent Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C367" s="5" t="inlineStr">
         <is>
-          <t>Smart Carbon Monoxide Alarm</t>
+          <t>Morelinks Thread Module (TN54AE)</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E367" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F367" s="4" t="inlineStr">
         <is>
-          <t>Gas alarm</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G367" s="5" t="inlineStr"/>
@@ -12343,27 +12343,27 @@
       </c>
       <c r="B368" s="7" t="inlineStr">
         <is>
-          <t>Shenzhen Heiman Technology Co., Ltd.</t>
+          <t>Shanghai Poyu Intelligent Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C368" s="7" t="inlineStr">
         <is>
-          <t>Smart Humidity &amp; Temperature Sensor</t>
+          <t>Morelinks Thread Module (TN54BE)</t>
         </is>
       </c>
       <c r="D368" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E368" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G368" s="7" t="inlineStr"/>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="B369" s="5" t="inlineStr">
         <is>
-          <t>Shenzhen Heiman Technology Co., Ltd.</t>
+          <t>Shenzhen Haojai Lianchuang Technology Co.,Ltd</t>
         </is>
       </c>
       <c r="C369" s="5" t="inlineStr">
         <is>
-          <t>Smart Plug (HS2SK series)</t>
+          <t>HAOJAI Smart Switch</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="F369" s="4" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G369" s="5" t="inlineStr"/>
@@ -12405,12 +12405,12 @@
       </c>
       <c r="B370" s="7" t="inlineStr">
         <is>
-          <t>Shenzhen Heiman Technology Co., Ltd.</t>
+          <t>Shenzhen Haojai Lianchuang Technology Co.,Ltd</t>
         </is>
       </c>
       <c r="C370" s="7" t="inlineStr">
         <is>
-          <t>Smart Smoke Alarm</t>
+          <t>Smart Curtain</t>
         </is>
       </c>
       <c r="D370" s="6" t="inlineStr">
@@ -12420,12 +12420,12 @@
       </c>
       <c r="E370" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>Smoke alarm</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G370" s="7" t="inlineStr"/>
@@ -12441,7 +12441,7 @@
       </c>
       <c r="C371" s="5" t="inlineStr">
         <is>
-          <t>Smart Water Leakage Sensor</t>
+          <t>Smart Carbon Monoxide Alarm</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E371" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F371" s="4" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Gas alarm</t>
         </is>
       </c>
       <c r="G371" s="5" t="inlineStr"/>
@@ -12467,27 +12467,27 @@
       </c>
       <c r="B372" s="7" t="inlineStr">
         <is>
-          <t>Shenzhen SDMC Technology Co., Ltd.</t>
+          <t>Shenzhen Heiman Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C372" s="7" t="inlineStr">
         <is>
-          <t>onn 4K Pro Streaming Device</t>
+          <t>Smart Humidity &amp; Temperature Sensor</t>
         </is>
       </c>
       <c r="D372" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E372" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>Media streamer</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G372" s="7" t="inlineStr"/>
@@ -12498,12 +12498,12 @@
       </c>
       <c r="B373" s="5" t="inlineStr">
         <is>
-          <t>Shenzhen Sonoff Technologies Co.,Ltd.</t>
+          <t>Shenzhen Heiman Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C373" s="5" t="inlineStr">
         <is>
-          <t>SONOFF Zigbee/Thread Motion Sensor</t>
+          <t>Smart Plug (HS2SK series)</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
@@ -12513,12 +12513,12 @@
       </c>
       <c r="E373" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F373" s="4" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Smart plug</t>
         </is>
       </c>
       <c r="G373" s="5" t="inlineStr"/>
@@ -12529,12 +12529,12 @@
       </c>
       <c r="B374" s="7" t="inlineStr">
         <is>
-          <t>Shenzhen Sonoff Technologies Co.,Ltd.</t>
+          <t>Shenzhen Heiman Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C374" s="7" t="inlineStr">
         <is>
-          <t>SONOFF Zigbee/Thread Temperature Sensor</t>
+          <t>Smart Smoke Alarm</t>
         </is>
       </c>
       <c r="D374" s="6" t="inlineStr">
@@ -12544,12 +12544,12 @@
       </c>
       <c r="E374" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Smoke alarm</t>
         </is>
       </c>
       <c r="G374" s="7" t="inlineStr"/>
@@ -12560,12 +12560,12 @@
       </c>
       <c r="B375" s="5" t="inlineStr">
         <is>
-          <t>Shenzhen Sonoff Technologies Co.,Ltd.</t>
+          <t>Shenzhen Heiman Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C375" s="5" t="inlineStr">
         <is>
-          <t>Zigbee/Thread Door Window Sensor</t>
+          <t>Smart Water Leakage Sensor</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F375" s="4" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G375" s="5" t="inlineStr"/>
@@ -12591,27 +12591,27 @@
       </c>
       <c r="B376" s="7" t="inlineStr">
         <is>
-          <t>Shenzhen Sunricher Technology Co.,Ltd.</t>
+          <t>Shenzhen SDMC Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C376" s="7" t="inlineStr">
         <is>
-          <t>Sensor &amp; Switch</t>
+          <t>onn 4K Pro Streaming Device</t>
         </is>
       </c>
       <c r="D376" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E376" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Media streamer</t>
         </is>
       </c>
       <c r="G376" s="7" t="inlineStr"/>
@@ -12622,12 +12622,12 @@
       </c>
       <c r="B377" s="5" t="inlineStr">
         <is>
-          <t>Shenzhen Sunricher Technology Co.,Ltd.</t>
+          <t>Shenzhen Sonoff Technologies Co.,Ltd.</t>
         </is>
       </c>
       <c r="C377" s="5" t="inlineStr">
         <is>
-          <t>Smart LED Dimmer Controller</t>
+          <t>SONOFF Zigbee/Thread Motion Sensor</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="E377" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F377" s="4" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G377" s="5" t="inlineStr"/>
@@ -12653,12 +12653,12 @@
       </c>
       <c r="B378" s="7" t="inlineStr">
         <is>
-          <t>Sichuan Changhong Neonet Technologies Co.,Ltd.</t>
+          <t>Shenzhen Sonoff Technologies Co.,Ltd.</t>
         </is>
       </c>
       <c r="C378" s="7" t="inlineStr">
         <is>
-          <t>Door Sensor</t>
+          <t>SONOFF Zigbee/Thread Temperature Sensor</t>
         </is>
       </c>
       <c r="D378" s="6" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G378" s="7" t="inlineStr"/>
@@ -12684,12 +12684,12 @@
       </c>
       <c r="B379" s="5" t="inlineStr">
         <is>
-          <t>Sichuan Changhong Neonet Technologies Co.,Ltd.</t>
+          <t>Shenzhen Sonoff Technologies Co.,Ltd.</t>
         </is>
       </c>
       <c r="C379" s="5" t="inlineStr">
         <is>
-          <t>Water Leak Detector</t>
+          <t>Zigbee/Thread Door Window Sensor</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="F379" s="4" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G379" s="5" t="inlineStr"/>
@@ -12715,27 +12715,27 @@
       </c>
       <c r="B380" s="7" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Shenzhen Sunricher Technology Co.,Ltd.</t>
         </is>
       </c>
       <c r="C380" s="7" t="inlineStr">
         <is>
-          <t>Thread Border Router</t>
+          <t>Sensor &amp; Switch</t>
         </is>
       </c>
       <c r="D380" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E380" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G380" s="7" t="inlineStr"/>
@@ -12746,12 +12746,12 @@
       </c>
       <c r="B381" s="5" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Shenzhen Sunricher Technology Co.,Ltd.</t>
         </is>
       </c>
       <c r="C381" s="5" t="inlineStr">
         <is>
-          <t>Wireless Room Sensor QAA2150KT</t>
+          <t>Smart LED Dimmer Controller</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
@@ -12761,12 +12761,12 @@
       </c>
       <c r="E381" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F381" s="4" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G381" s="5" t="inlineStr"/>
@@ -12777,12 +12777,12 @@
       </c>
       <c r="B382" s="7" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Sichuan Changhong Neonet Technologies Co.,Ltd.</t>
         </is>
       </c>
       <c r="C382" s="7" t="inlineStr">
         <is>
-          <t>Wireless Room Sensor QAA2890/WI</t>
+          <t>Door Sensor</t>
         </is>
       </c>
       <c r="D382" s="6" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G382" s="7" t="inlineStr"/>
@@ -12808,12 +12808,12 @@
       </c>
       <c r="B383" s="5" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Sichuan Changhong Neonet Technologies Co.,Ltd.</t>
         </is>
       </c>
       <c r="C383" s="5" t="inlineStr">
         <is>
-          <t>Wireless Room Sensor QFA2250KT</t>
+          <t>Water Leak Detector</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="F383" s="4" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G383" s="5" t="inlineStr"/>
@@ -12844,22 +12844,22 @@
       </c>
       <c r="C384" s="7" t="inlineStr">
         <is>
-          <t>Wireless Room Sensor QFA2890/WI</t>
+          <t>Thread Border Router</t>
         </is>
       </c>
       <c r="D384" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E384" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G384" s="7" t="inlineStr"/>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="C385" s="5" t="inlineStr">
         <is>
-          <t>Wireless Room Sensor QPA2350KT</t>
+          <t>Wireless Room Sensor QAA2150KT</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="C386" s="7" t="inlineStr">
         <is>
-          <t>Wireless Room Sensor QPA2892/WI</t>
+          <t>Wireless Room Sensor QAA2890/WI</t>
         </is>
       </c>
       <c r="D386" s="6" t="inlineStr">
@@ -12932,12 +12932,12 @@
       </c>
       <c r="B387" s="5" t="inlineStr">
         <is>
-          <t>Signify Netherlands B.V.</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C387" s="5" t="inlineStr">
         <is>
-          <t>Philips Hue Light</t>
+          <t>Wireless Room Sensor QFA2250KT</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -12947,12 +12947,12 @@
       </c>
       <c r="E387" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F387" s="4" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G387" s="5" t="inlineStr"/>
@@ -12963,27 +12963,27 @@
       </c>
       <c r="B388" s="7" t="inlineStr">
         <is>
-          <t>Silicon Laboratories, Inc.</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C388" s="7" t="inlineStr">
         <is>
-          <t>MGM12P</t>
+          <t>Wireless Room Sensor QFA2890/WI</t>
         </is>
       </c>
       <c r="D388" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E388" s="6" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G388" s="7" t="inlineStr"/>
@@ -12994,27 +12994,27 @@
       </c>
       <c r="B389" s="5" t="inlineStr">
         <is>
-          <t>Silicon Laboratories, Inc.</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C389" s="5" t="inlineStr">
         <is>
-          <t>Silicon Labs Mighty Gecko (EFR32MG12x)</t>
+          <t>Wireless Room Sensor QPA2350KT</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E389" s="4" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F389" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G389" s="5" t="inlineStr"/>
@@ -13025,27 +13025,27 @@
       </c>
       <c r="B390" s="7" t="inlineStr">
         <is>
-          <t>Silicon Laboratories, Inc.</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C390" s="7" t="inlineStr">
         <is>
-          <t>Silicon Labs Mighty Gecko (EFR32MG13x)</t>
+          <t>Wireless Room Sensor QPA2892/WI</t>
         </is>
       </c>
       <c r="D390" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E390" s="6" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G390" s="7" t="inlineStr"/>
@@ -13056,27 +13056,27 @@
       </c>
       <c r="B391" s="5" t="inlineStr">
         <is>
-          <t>Silicon Laboratories, Inc.</t>
+          <t>Signify Netherlands B.V.</t>
         </is>
       </c>
       <c r="C391" s="5" t="inlineStr">
         <is>
-          <t>Silicon Labs Mighty Gecko (EFR32MG21x)</t>
+          <t>Philips Hue Light</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E391" s="4" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F391" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G391" s="5" t="inlineStr"/>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="C392" s="7" t="inlineStr">
         <is>
-          <t>Silicon Labs Mighty Gecko (EFR32MG24x)</t>
+          <t>MGM12P</t>
         </is>
       </c>
       <c r="D392" s="6" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="E392" s="6" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F392" s="6" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="C393" s="5" t="inlineStr">
         <is>
-          <t>Silicon Labs Mighty Gecko (EFR32MG26x)</t>
+          <t>Silicon Labs Mighty Gecko (EFR32MG12x)</t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="C394" s="7" t="inlineStr">
         <is>
-          <t>Silicon Labs Mighty Gecko (SiMG301)</t>
+          <t>Silicon Labs Mighty Gecko (EFR32MG13x)</t>
         </is>
       </c>
       <c r="D394" s="6" t="inlineStr">
@@ -13180,27 +13180,27 @@
       </c>
       <c r="B395" s="5" t="inlineStr">
         <is>
-          <t>Siterwell Electronics Co., Limited</t>
+          <t>Silicon Laboratories, Inc.</t>
         </is>
       </c>
       <c r="C395" s="5" t="inlineStr">
         <is>
-          <t>Smoke CO Alarm</t>
+          <t>Silicon Labs Mighty Gecko (EFR32MG21x)</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E395" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F395" s="4" t="inlineStr">
         <is>
-          <t>Smoke alarm</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G395" s="5" t="inlineStr"/>
@@ -13211,22 +13211,22 @@
       </c>
       <c r="B396" s="7" t="inlineStr">
         <is>
-          <t>Skylux NV</t>
+          <t>Silicon Laboratories, Inc.</t>
         </is>
       </c>
       <c r="C396" s="7" t="inlineStr">
         <is>
-          <t>Screen</t>
+          <t>Silicon Labs Mighty Gecko (EFR32MG24x)</t>
         </is>
       </c>
       <c r="D396" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E396" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F396" s="6" t="inlineStr">
@@ -13242,22 +13242,22 @@
       </c>
       <c r="B397" s="5" t="inlineStr">
         <is>
-          <t>Skylux NV</t>
+          <t>Silicon Laboratories, Inc.</t>
         </is>
       </c>
       <c r="C397" s="5" t="inlineStr">
         <is>
-          <t>iWindow</t>
+          <t>Silicon Labs Mighty Gecko (EFR32MG26x)</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E397" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F397" s="4" t="inlineStr">
@@ -13273,27 +13273,27 @@
       </c>
       <c r="B398" s="7" t="inlineStr">
         <is>
-          <t>Sleekpoint Innovations Company Limited</t>
+          <t>Silicon Laboratories, Inc.</t>
         </is>
       </c>
       <c r="C398" s="7" t="inlineStr">
         <is>
-          <t>Airversa Purelle Smart Air Purifier</t>
+          <t>Silicon Labs Mighty Gecko (SiMG301)</t>
         </is>
       </c>
       <c r="D398" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E398" s="6" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F398" s="6" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G398" s="7" t="inlineStr"/>
@@ -13304,12 +13304,12 @@
       </c>
       <c r="B399" s="5" t="inlineStr">
         <is>
-          <t>Sleekpoint Innovations Company Limited</t>
+          <t>Siterwell Electronics Co., Limited</t>
         </is>
       </c>
       <c r="C399" s="5" t="inlineStr">
         <is>
-          <t>Button Controller</t>
+          <t>Smoke CO Alarm</t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="E399" s="4" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F399" s="4" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Smoke alarm</t>
         </is>
       </c>
       <c r="G399" s="5" t="inlineStr"/>
@@ -13335,12 +13335,12 @@
       </c>
       <c r="B400" s="7" t="inlineStr">
         <is>
-          <t>Sleekpoint Innovations Company Limited</t>
+          <t>Skylux NV</t>
         </is>
       </c>
       <c r="C400" s="7" t="inlineStr">
         <is>
-          <t>Smart Lock</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="D400" s="6" t="inlineStr">
@@ -13350,12 +13350,12 @@
       </c>
       <c r="E400" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F400" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G400" s="7" t="inlineStr"/>
@@ -13366,12 +13366,12 @@
       </c>
       <c r="B401" s="5" t="inlineStr">
         <is>
-          <t>SmartWings Home LLC</t>
+          <t>Skylux NV</t>
         </is>
       </c>
       <c r="C401" s="5" t="inlineStr">
         <is>
-          <t>SmartWings window covering</t>
+          <t>iWindow</t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
@@ -13381,12 +13381,12 @@
       </c>
       <c r="E401" s="4" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F401" s="4" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G401" s="5" t="inlineStr"/>
@@ -13397,12 +13397,12 @@
       </c>
       <c r="B402" s="7" t="inlineStr">
         <is>
-          <t>TETNET OÜ</t>
+          <t>Sleekpoint Innovations Company Limited</t>
         </is>
       </c>
       <c r="C402" s="7" t="inlineStr">
         <is>
-          <t>Tarken WM</t>
+          <t>Airversa Purelle Smart Air Purifier</t>
         </is>
       </c>
       <c r="D402" s="6" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="E402" s="6" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F402" s="6" t="inlineStr">
         <is>
-          <t>Window lock</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="G402" s="7" t="inlineStr"/>
@@ -13428,12 +13428,12 @@
       </c>
       <c r="B403" s="5" t="inlineStr">
         <is>
-          <t>Tedee Sp. z o.o.</t>
+          <t>Sleekpoint Innovations Company Limited</t>
         </is>
       </c>
       <c r="C403" s="5" t="inlineStr">
         <is>
-          <t>Tedee GO</t>
+          <t>Button Controller</t>
         </is>
       </c>
       <c r="D403" s="4" t="inlineStr">
@@ -13443,12 +13443,12 @@
       </c>
       <c r="E403" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F403" s="4" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G403" s="5" t="inlineStr"/>
@@ -13459,27 +13459,27 @@
       </c>
       <c r="B404" s="7" t="inlineStr">
         <is>
-          <t>Telink Semiconductor (Shanghai) Co., Ltd.</t>
+          <t>Sleekpoint Innovations Company Limited</t>
         </is>
       </c>
       <c r="C404" s="7" t="inlineStr">
         <is>
-          <t>TL323X Series SoC</t>
+          <t>Smart Lock</t>
         </is>
       </c>
       <c r="D404" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E404" s="6" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F404" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G404" s="7" t="inlineStr"/>
@@ -13490,27 +13490,27 @@
       </c>
       <c r="B405" s="5" t="inlineStr">
         <is>
-          <t>Telink Semiconductor (Shanghai) Co., Ltd.</t>
+          <t>SmartWings Home LLC</t>
         </is>
       </c>
       <c r="C405" s="5" t="inlineStr">
         <is>
-          <t>TLSR9</t>
+          <t>SmartWings window covering</t>
         </is>
       </c>
       <c r="D405" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E405" s="4" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F405" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G405" s="5" t="inlineStr"/>
@@ -13521,27 +13521,27 @@
       </c>
       <c r="B406" s="7" t="inlineStr">
         <is>
-          <t>Telink Semiconductor (Shanghai) Co., Ltd.</t>
+          <t>TETNET OÜ</t>
         </is>
       </c>
       <c r="C406" s="7" t="inlineStr">
         <is>
-          <t>TLSR9 - Border Router</t>
+          <t>Tarken WM</t>
         </is>
       </c>
       <c r="D406" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E406" s="6" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F406" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Window lock</t>
         </is>
       </c>
       <c r="G406" s="7" t="inlineStr"/>
@@ -13552,27 +13552,27 @@
       </c>
       <c r="B407" s="5" t="inlineStr">
         <is>
-          <t>Telink Semiconductor (Shanghai) Co., Ltd.</t>
+          <t>Tedee Sp. z o.o.</t>
         </is>
       </c>
       <c r="C407" s="5" t="inlineStr">
         <is>
-          <t>TLSR922X Series SoC</t>
+          <t>Tedee GO</t>
         </is>
       </c>
       <c r="D407" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E407" s="4" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F407" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G407" s="5" t="inlineStr"/>
@@ -13583,12 +13583,12 @@
       </c>
       <c r="B408" s="7" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc.</t>
+          <t>Telink Semiconductor (Shanghai) Co., Ltd.</t>
         </is>
       </c>
       <c r="C408" s="7" t="inlineStr">
         <is>
-          <t>CC2674x_1354x</t>
+          <t>TL323X Series SoC</t>
         </is>
       </c>
       <c r="D408" s="6" t="inlineStr">
@@ -13614,12 +13614,12 @@
       </c>
       <c r="B409" s="5" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc.</t>
+          <t>Telink Semiconductor (Shanghai) Co., Ltd.</t>
         </is>
       </c>
       <c r="C409" s="5" t="inlineStr">
         <is>
-          <t>CC26x2</t>
+          <t>TLSR9</t>
         </is>
       </c>
       <c r="D409" s="4" t="inlineStr">
@@ -13645,12 +13645,12 @@
       </c>
       <c r="B410" s="7" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc.</t>
+          <t>Telink Semiconductor (Shanghai) Co., Ltd.</t>
         </is>
       </c>
       <c r="C410" s="7" t="inlineStr">
         <is>
-          <t>EOL - CC1352R/P</t>
+          <t>TLSR9 - Border Router</t>
         </is>
       </c>
       <c r="D410" s="6" t="inlineStr">
@@ -13676,27 +13676,27 @@
       </c>
       <c r="B411" s="5" t="inlineStr">
         <is>
-          <t>ThirdReality, Inc.</t>
+          <t>Telink Semiconductor (Shanghai) Co., Ltd.</t>
         </is>
       </c>
       <c r="C411" s="5" t="inlineStr">
         <is>
-          <t>Smart Night Light-T</t>
+          <t>TLSR922X Series SoC</t>
         </is>
       </c>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E411" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F411" s="4" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G411" s="5" t="inlineStr"/>
@@ -13707,27 +13707,27 @@
       </c>
       <c r="B412" s="7" t="inlineStr">
         <is>
-          <t>ThirdReality, Inc.</t>
+          <t>Texas Instruments Inc.</t>
         </is>
       </c>
       <c r="C412" s="7" t="inlineStr">
         <is>
-          <t>Smart Switch MT1</t>
+          <t>CC2674x_1354x</t>
         </is>
       </c>
       <c r="D412" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E412" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F412" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G412" s="7" t="inlineStr"/>
@@ -13738,27 +13738,27 @@
       </c>
       <c r="B413" s="5" t="inlineStr">
         <is>
-          <t>Tuya Global Inc</t>
+          <t>Texas Instruments Inc.</t>
         </is>
       </c>
       <c r="C413" s="5" t="inlineStr">
         <is>
-          <t>Door Window Sensor</t>
+          <t>CC26x2</t>
         </is>
       </c>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E413" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F413" s="4" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G413" s="5" t="inlineStr"/>
@@ -13769,27 +13769,27 @@
       </c>
       <c r="B414" s="7" t="inlineStr">
         <is>
-          <t>Tuya Global Inc</t>
+          <t>Texas Instruments Inc.</t>
         </is>
       </c>
       <c r="C414" s="7" t="inlineStr">
         <is>
-          <t>Motion Sensor</t>
+          <t>EOL - CC1352R/P</t>
         </is>
       </c>
       <c r="D414" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E414" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F414" s="6" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G414" s="7" t="inlineStr"/>
@@ -13800,12 +13800,12 @@
       </c>
       <c r="B415" s="5" t="inlineStr">
         <is>
-          <t>Tuya Global Inc</t>
+          <t>ThirdReality, Inc.</t>
         </is>
       </c>
       <c r="C415" s="5" t="inlineStr">
         <is>
-          <t>Smart Door Lock</t>
+          <t>Smart Night Light-T</t>
         </is>
       </c>
       <c r="D415" s="4" t="inlineStr">
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E415" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F415" s="4" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G415" s="5" t="inlineStr"/>
@@ -13831,12 +13831,12 @@
       </c>
       <c r="B416" s="7" t="inlineStr">
         <is>
-          <t>Tuya Global Inc</t>
+          <t>ThirdReality, Inc.</t>
         </is>
       </c>
       <c r="C416" s="7" t="inlineStr">
         <is>
-          <t>Smart Window Covering</t>
+          <t>Smart Switch MT1</t>
         </is>
       </c>
       <c r="D416" s="6" t="inlineStr">
@@ -13846,12 +13846,12 @@
       </c>
       <c r="E416" s="6" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F416" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G416" s="7" t="inlineStr"/>
@@ -13867,22 +13867,22 @@
       </c>
       <c r="C417" s="5" t="inlineStr">
         <is>
-          <t>TS24-LC5</t>
+          <t>Door Window Sensor</t>
         </is>
       </c>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E417" s="4" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F417" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G417" s="5" t="inlineStr"/>
@@ -13898,22 +13898,22 @@
       </c>
       <c r="C418" s="7" t="inlineStr">
         <is>
-          <t>TS24-U</t>
+          <t>Motion Sensor</t>
         </is>
       </c>
       <c r="D418" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E418" s="6" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F418" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G418" s="7" t="inlineStr"/>
@@ -13929,22 +13929,22 @@
       </c>
       <c r="C419" s="5" t="inlineStr">
         <is>
-          <t>TS24-U-IPEX</t>
+          <t>Smart Door Lock</t>
         </is>
       </c>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E419" s="4" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F419" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G419" s="5" t="inlineStr"/>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="C420" s="7" t="inlineStr">
         <is>
-          <t>Thread Bulb</t>
+          <t>Smart Window Covering</t>
         </is>
       </c>
       <c r="D420" s="6" t="inlineStr">
@@ -13970,12 +13970,12 @@
       </c>
       <c r="E420" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F420" s="6" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G420" s="7" t="inlineStr"/>
@@ -13991,17 +13991,17 @@
       </c>
       <c r="C421" s="5" t="inlineStr">
         <is>
-          <t>Thread Color Temperature Light Drive</t>
+          <t>TS24-LC5</t>
         </is>
       </c>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E421" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F421" s="4" t="inlineStr">
@@ -14022,17 +14022,17 @@
       </c>
       <c r="C422" s="7" t="inlineStr">
         <is>
-          <t>Thread Dimmable Light Drive</t>
+          <t>TS24-U</t>
         </is>
       </c>
       <c r="D422" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E422" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F422" s="6" t="inlineStr">
@@ -14053,7 +14053,7 @@
       </c>
       <c r="C423" s="5" t="inlineStr">
         <is>
-          <t>Wireless Module E2-U</t>
+          <t>TS24-U-IPEX</t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="B424" s="7" t="inlineStr">
         <is>
-          <t>Vitrumshade LLC</t>
+          <t>Tuya Global Inc</t>
         </is>
       </c>
       <c r="C424" s="7" t="inlineStr">
         <is>
-          <t>Smart Internal Blinds</t>
+          <t>Thread Bulb</t>
         </is>
       </c>
       <c r="D424" s="6" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="E424" s="6" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F424" s="6" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="G424" s="7" t="inlineStr"/>
@@ -14110,12 +14110,12 @@
       </c>
       <c r="B425" s="5" t="inlineStr">
         <is>
-          <t>WAREMA Renkhoff SE</t>
+          <t>Tuya Global Inc</t>
         </is>
       </c>
       <c r="C425" s="5" t="inlineStr">
         <is>
-          <t>Xeenos Go Aktor Jalousie Plug</t>
+          <t>Thread Color Temperature Light Drive</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
@@ -14125,12 +14125,12 @@
       </c>
       <c r="E425" s="4" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F425" s="4" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G425" s="5" t="inlineStr"/>
@@ -14141,12 +14141,12 @@
       </c>
       <c r="B426" s="7" t="inlineStr">
         <is>
-          <t>WAREMA Renkhoff SE</t>
+          <t>Tuya Global Inc</t>
         </is>
       </c>
       <c r="C426" s="7" t="inlineStr">
         <is>
-          <t>Xeenos Go Aktor Jalousie UP</t>
+          <t>Thread Dimmable Light Drive</t>
         </is>
       </c>
       <c r="D426" s="6" t="inlineStr">
@@ -14156,12 +14156,12 @@
       </c>
       <c r="E426" s="6" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F426" s="6" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G426" s="7" t="inlineStr"/>
@@ -14172,27 +14172,27 @@
       </c>
       <c r="B427" s="5" t="inlineStr">
         <is>
-          <t>WAREMA Renkhoff SE</t>
+          <t>Tuya Global Inc</t>
         </is>
       </c>
       <c r="C427" s="5" t="inlineStr">
         <is>
-          <t>Xeenos Go Aktor Rollladen Plug</t>
+          <t>Wireless Module E2-U</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E427" s="4" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F427" s="4" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G427" s="5" t="inlineStr"/>
@@ -14203,12 +14203,12 @@
       </c>
       <c r="B428" s="7" t="inlineStr">
         <is>
-          <t>WAREMA Renkhoff SE</t>
+          <t>Vitrumshade LLC</t>
         </is>
       </c>
       <c r="C428" s="7" t="inlineStr">
         <is>
-          <t>Xeenos Go Aktor Rollladen UP</t>
+          <t>Smart Internal Blinds</t>
         </is>
       </c>
       <c r="D428" s="6" t="inlineStr">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="F428" s="6" t="inlineStr">
         <is>
-          <t>Shutter</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G428" s="7" t="inlineStr"/>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="C429" s="5" t="inlineStr">
         <is>
-          <t>Xeenos Go Aktor Switch 2K UP</t>
+          <t>Xeenos Go Aktor Jalousie Plug</t>
         </is>
       </c>
       <c r="D429" s="4" t="inlineStr">
@@ -14249,12 +14249,12 @@
       </c>
       <c r="E429" s="4" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F429" s="4" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G429" s="5" t="inlineStr"/>
@@ -14265,12 +14265,12 @@
       </c>
       <c r="B430" s="7" t="inlineStr">
         <is>
-          <t>WINTECKOREA INC</t>
+          <t>WAREMA Renkhoff SE</t>
         </is>
       </c>
       <c r="C430" s="7" t="inlineStr">
         <is>
-          <t>GATEWAY-MT</t>
+          <t>Xeenos Go Aktor Jalousie UP</t>
         </is>
       </c>
       <c r="D430" s="6" t="inlineStr">
@@ -14296,12 +14296,12 @@
       </c>
       <c r="B431" s="5" t="inlineStr">
         <is>
-          <t>WNC Corporation</t>
+          <t>WAREMA Renkhoff SE</t>
         </is>
       </c>
       <c r="C431" s="5" t="inlineStr">
         <is>
-          <t>Indoor Air Quality Monitor</t>
+          <t>Xeenos Go Aktor Rollladen Plug</t>
         </is>
       </c>
       <c r="D431" s="4" t="inlineStr">
@@ -14311,12 +14311,12 @@
       </c>
       <c r="E431" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F431" s="4" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G431" s="5" t="inlineStr"/>
@@ -14327,12 +14327,12 @@
       </c>
       <c r="B432" s="7" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>WAREMA Renkhoff SE</t>
         </is>
       </c>
       <c r="C432" s="7" t="inlineStr">
         <is>
-          <t>Tekmar Smart Steam Control 289</t>
+          <t>Xeenos Go Aktor Rollladen UP</t>
         </is>
       </c>
       <c r="D432" s="6" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="E432" s="6" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F432" s="6" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>Shutter</t>
         </is>
       </c>
       <c r="G432" s="7" t="inlineStr"/>
@@ -14358,12 +14358,12 @@
       </c>
       <c r="B433" s="5" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>WAREMA Renkhoff SE</t>
         </is>
       </c>
       <c r="C433" s="5" t="inlineStr">
         <is>
-          <t>tekmar Smart Boiler Control 294</t>
+          <t>Xeenos Go Aktor Switch 2K UP</t>
         </is>
       </c>
       <c r="D433" s="4" t="inlineStr">
@@ -14373,12 +14373,12 @@
       </c>
       <c r="E433" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F433" s="4" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G433" s="5" t="inlineStr"/>
@@ -14389,12 +14389,12 @@
       </c>
       <c r="B434" s="7" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>WINTECKOREA INC</t>
         </is>
       </c>
       <c r="C434" s="7" t="inlineStr">
         <is>
-          <t>tekmar Wireless Mesh Indoor Sensor 042</t>
+          <t>GATEWAY-MT</t>
         </is>
       </c>
       <c r="D434" s="6" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="E434" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F434" s="6" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G434" s="7" t="inlineStr"/>
@@ -14420,12 +14420,12 @@
       </c>
       <c r="B435" s="5" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>WNC Corporation</t>
         </is>
       </c>
       <c r="C435" s="5" t="inlineStr">
         <is>
-          <t>tekmar Wireless Mesh Outdoor Sensor 043</t>
+          <t>Indoor Air Quality Monitor</t>
         </is>
       </c>
       <c r="D435" s="4" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="F435" s="4" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="G435" s="5" t="inlineStr"/>
@@ -14451,12 +14451,12 @@
       </c>
       <c r="B436" s="7" t="inlineStr">
         <is>
-          <t>What's Matter Inc.</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C436" s="7" t="inlineStr">
         <is>
-          <t>Air Quality Sensor</t>
+          <t>Tekmar Smart Steam Control 289</t>
         </is>
       </c>
       <c r="D436" s="6" t="inlineStr">
@@ -14466,12 +14466,12 @@
       </c>
       <c r="E436" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F436" s="6" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Heating</t>
         </is>
       </c>
       <c r="G436" s="7" t="inlineStr"/>
@@ -14482,12 +14482,12 @@
       </c>
       <c r="B437" s="5" t="inlineStr">
         <is>
-          <t>What's Matter Inc.</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C437" s="5" t="inlineStr">
         <is>
-          <t>Light Sensor</t>
+          <t>tekmar Smart Boiler Control 294</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr">
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E437" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F437" s="4" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Heating</t>
         </is>
       </c>
       <c r="G437" s="5" t="inlineStr"/>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="B438" s="7" t="inlineStr">
         <is>
-          <t>What's Matter Inc.</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C438" s="7" t="inlineStr">
         <is>
-          <t>Radar Presence Sensor</t>
+          <t>tekmar Wireless Mesh Indoor Sensor 042</t>
         </is>
       </c>
       <c r="D438" s="6" t="inlineStr">
@@ -14533,7 +14533,7 @@
       </c>
       <c r="F438" s="6" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G438" s="7" t="inlineStr"/>
@@ -14544,17 +14544,17 @@
       </c>
       <c r="B439" s="5" t="inlineStr">
         <is>
-          <t>What's Matter Inc.</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C439" s="5" t="inlineStr">
         <is>
-          <t>Smoke Sensor</t>
+          <t>tekmar Wireless Mesh Outdoor Sensor 043</t>
         </is>
       </c>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E439" s="4" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="F439" s="4" t="inlineStr">
         <is>
-          <t>Smoke alarm</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G439" s="5" t="inlineStr"/>
@@ -14580,7 +14580,7 @@
       </c>
       <c r="C440" s="7" t="inlineStr">
         <is>
-          <t>Temperature and Humidity Sensor</t>
+          <t>Air Quality Sensor</t>
         </is>
       </c>
       <c r="D440" s="6" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="F440" s="6" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="G440" s="7" t="inlineStr"/>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C441" s="5" t="inlineStr">
         <is>
-          <t>Vibration Sensor</t>
+          <t>Light Sensor</t>
         </is>
       </c>
       <c r="D441" s="4" t="inlineStr">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="F441" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G441" s="5" t="inlineStr"/>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="C442" s="7" t="inlineStr">
         <is>
-          <t>Window and Door Sensor</t>
+          <t>Radar Presence Sensor</t>
         </is>
       </c>
       <c r="D442" s="6" t="inlineStr">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="F442" s="6" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G442" s="7" t="inlineStr"/>
@@ -14668,27 +14668,27 @@
       </c>
       <c r="B443" s="5" t="inlineStr">
         <is>
-          <t>WideSky.cloud Pty. Ltd</t>
+          <t>What's Matter Inc.</t>
         </is>
       </c>
       <c r="C443" s="5" t="inlineStr">
         <is>
-          <t>WideSky Hub</t>
+          <t>Smoke Sensor</t>
         </is>
       </c>
       <c r="D443" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E443" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F443" s="4" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Smoke alarm</t>
         </is>
       </c>
       <c r="G443" s="5" t="inlineStr"/>
@@ -14699,12 +14699,12 @@
       </c>
       <c r="B444" s="7" t="inlineStr">
         <is>
-          <t>Xiaomi Communications Co., Ltd.</t>
+          <t>What's Matter Inc.</t>
         </is>
       </c>
       <c r="C444" s="7" t="inlineStr">
         <is>
-          <t>Xiaomi Self-Install Smart Lock (Keypad Included)</t>
+          <t>Temperature and Humidity Sensor</t>
         </is>
       </c>
       <c r="D444" s="6" t="inlineStr">
@@ -14714,12 +14714,12 @@
       </c>
       <c r="E444" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F444" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="G444" s="7" t="inlineStr"/>
@@ -14730,12 +14730,12 @@
       </c>
       <c r="B445" s="5" t="inlineStr">
         <is>
-          <t>Xthings Industry</t>
+          <t>What's Matter Inc.</t>
         </is>
       </c>
       <c r="C445" s="5" t="inlineStr">
         <is>
-          <t>ULTRALOQ Bolt Fingerprint and NFC Smart Matter Deadbolt</t>
+          <t>Vibration Sensor</t>
         </is>
       </c>
       <c r="D445" s="4" t="inlineStr">
@@ -14745,12 +14745,12 @@
       </c>
       <c r="E445" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F445" s="4" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G445" s="5" t="inlineStr"/>
@@ -14761,12 +14761,12 @@
       </c>
       <c r="B446" s="7" t="inlineStr">
         <is>
-          <t>Xthings Industry</t>
+          <t>What's Matter Inc.</t>
         </is>
       </c>
       <c r="C446" s="7" t="inlineStr">
         <is>
-          <t>ULTRALOQ Bolt NFC Smart Matter Deadbolt</t>
+          <t>WM 2Gang Smart Button</t>
         </is>
       </c>
       <c r="D446" s="6" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="E446" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F446" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G446" s="7" t="inlineStr"/>
@@ -14792,12 +14792,12 @@
       </c>
       <c r="B447" s="5" t="inlineStr">
         <is>
-          <t>Xthings Industry</t>
+          <t>What's Matter Inc.</t>
         </is>
       </c>
       <c r="C447" s="5" t="inlineStr">
         <is>
-          <t>ULTRALOQ Latch5 Fingerprint Smart Matter Lever</t>
+          <t>WM CO2 Sensor</t>
         </is>
       </c>
       <c r="D447" s="4" t="inlineStr">
@@ -14807,12 +14807,12 @@
       </c>
       <c r="E447" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F447" s="4" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="G447" s="5" t="inlineStr"/>
@@ -14823,12 +14823,12 @@
       </c>
       <c r="B448" s="7" t="inlineStr">
         <is>
-          <t>Xthings Industry</t>
+          <t>What's Matter Inc.</t>
         </is>
       </c>
       <c r="C448" s="7" t="inlineStr">
         <is>
-          <t>ULTRALOQ U-Bolt Pro Smart Matter Deadbolt</t>
+          <t>WM Radar Presence Sensor 2</t>
         </is>
       </c>
       <c r="D448" s="6" t="inlineStr">
@@ -14838,12 +14838,12 @@
       </c>
       <c r="E448" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F448" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G448" s="7" t="inlineStr"/>
@@ -14854,12 +14854,12 @@
       </c>
       <c r="B449" s="5" t="inlineStr">
         <is>
-          <t>Xthings Industry</t>
+          <t>What's Matter Inc.</t>
         </is>
       </c>
       <c r="C449" s="5" t="inlineStr">
         <is>
-          <t>ULTRALOQ U-bolt Smart Matter Deadbolt</t>
+          <t>WM Water Leak Detector</t>
         </is>
       </c>
       <c r="D449" s="4" t="inlineStr">
@@ -14869,12 +14869,12 @@
       </c>
       <c r="E449" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F449" s="4" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G449" s="5" t="inlineStr"/>
@@ -14885,12 +14885,12 @@
       </c>
       <c r="B450" s="7" t="inlineStr">
         <is>
-          <t>Xthings Industry</t>
+          <t>What's Matter Inc.</t>
         </is>
       </c>
       <c r="C450" s="7" t="inlineStr">
         <is>
-          <t>Ultraloq Bolt Fingerprint Smart Matter Deadbolt</t>
+          <t>Window and Door Sensor</t>
         </is>
       </c>
       <c r="D450" s="6" t="inlineStr">
@@ -14900,12 +14900,12 @@
       </c>
       <c r="E450" s="6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F450" s="6" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G450" s="7" t="inlineStr"/>
@@ -14916,12 +14916,12 @@
       </c>
       <c r="B451" s="5" t="inlineStr">
         <is>
-          <t>ZIMI INNOVATIONS PTY LTD</t>
+          <t>WideSky.cloud Pty. Ltd</t>
         </is>
       </c>
       <c r="C451" s="5" t="inlineStr">
         <is>
-          <t>Senoa Matter Power Point</t>
+          <t>WideSky Hub</t>
         </is>
       </c>
       <c r="D451" s="4" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="E451" s="4" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F451" s="4" t="inlineStr">
         <is>
-          <t>Smart plug</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G451" s="5" t="inlineStr"/>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B452" s="7" t="inlineStr">
         <is>
-          <t>ZIMI INNOVATIONS PTY LTD</t>
+          <t>Xiaomi Communications Co., Ltd.</t>
         </is>
       </c>
       <c r="C452" s="7" t="inlineStr">
         <is>
-          <t>Senoa Matter Switch</t>
+          <t>Xiaomi Self-Install Smart Lock (Keypad Included)</t>
         </is>
       </c>
       <c r="D452" s="6" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E452" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F452" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G452" s="7" t="inlineStr"/>
@@ -14978,12 +14978,12 @@
       </c>
       <c r="B453" s="5" t="inlineStr">
         <is>
-          <t>Zemismart Technology Limited</t>
+          <t>Xthings Industry</t>
         </is>
       </c>
       <c r="C453" s="5" t="inlineStr">
         <is>
-          <t>Zemismart Lighting Kit</t>
+          <t>ULTRALOQ Bolt Fingerprint and NFC Smart Matter Deadbolt</t>
         </is>
       </c>
       <c r="D453" s="4" t="inlineStr">
@@ -14993,12 +14993,12 @@
       </c>
       <c r="E453" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F453" s="4" t="inlineStr">
         <is>
-          <t>Lightstrip</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G453" s="5" t="inlineStr"/>
@@ -15009,12 +15009,12 @@
       </c>
       <c r="B454" s="7" t="inlineStr">
         <is>
-          <t>Zemismart Technology Limited</t>
+          <t>Xthings Industry</t>
         </is>
       </c>
       <c r="C454" s="7" t="inlineStr">
         <is>
-          <t>Zemismart MT01 Slide Curtain</t>
+          <t>ULTRALOQ Bolt NFC Smart Matter Deadbolt</t>
         </is>
       </c>
       <c r="D454" s="6" t="inlineStr">
@@ -15024,12 +15024,12 @@
       </c>
       <c r="E454" s="6" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F454" s="6" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G454" s="7" t="inlineStr"/>
@@ -15040,12 +15040,12 @@
       </c>
       <c r="B455" s="5" t="inlineStr">
         <is>
-          <t>Zemismart Technology Limited</t>
+          <t>Xthings Industry</t>
         </is>
       </c>
       <c r="C455" s="5" t="inlineStr">
         <is>
-          <t>Zemismart Motion Detector</t>
+          <t>ULTRALOQ Latch5 Fingerprint Smart Matter Lever</t>
         </is>
       </c>
       <c r="D455" s="4" t="inlineStr">
@@ -15055,12 +15055,12 @@
       </c>
       <c r="E455" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F455" s="4" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G455" s="5" t="inlineStr"/>
@@ -15071,12 +15071,12 @@
       </c>
       <c r="B456" s="7" t="inlineStr">
         <is>
-          <t>Zemismart Technology Limited</t>
+          <t>Xthings Industry</t>
         </is>
       </c>
       <c r="C456" s="7" t="inlineStr">
         <is>
-          <t>Zemismart Thread Curtain Motor</t>
+          <t>ULTRALOQ U-Bolt Pro Smart Matter Deadbolt</t>
         </is>
       </c>
       <c r="D456" s="6" t="inlineStr">
@@ -15086,12 +15086,12 @@
       </c>
       <c r="E456" s="6" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F456" s="6" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G456" s="7" t="inlineStr"/>
@@ -15102,12 +15102,12 @@
       </c>
       <c r="B457" s="5" t="inlineStr">
         <is>
-          <t>Zemismart Technology Limited</t>
+          <t>Xthings Industry</t>
         </is>
       </c>
       <c r="C457" s="5" t="inlineStr">
         <is>
-          <t>Zemismart Window Shading System Driver</t>
+          <t>ULTRALOQ U-bolt Smart Matter Deadbolt</t>
         </is>
       </c>
       <c r="D457" s="4" t="inlineStr">
@@ -15117,12 +15117,12 @@
       </c>
       <c r="E457" s="4" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F457" s="4" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G457" s="5" t="inlineStr"/>
@@ -15133,12 +15133,12 @@
       </c>
       <c r="B458" s="7" t="inlineStr">
         <is>
-          <t>Zhejiang General light Curtain Co., Ltd.</t>
+          <t>Xthings Industry</t>
         </is>
       </c>
       <c r="C458" s="7" t="inlineStr">
         <is>
-          <t>25 DC roller shutter motor</t>
+          <t>Ultraloq Bolt Fingerprint Smart Matter Deadbolt</t>
         </is>
       </c>
       <c r="D458" s="6" t="inlineStr">
@@ -15148,12 +15148,12 @@
       </c>
       <c r="E458" s="6" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F458" s="6" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="G458" s="7" t="inlineStr"/>
@@ -15164,12 +15164,12 @@
       </c>
       <c r="B459" s="5" t="inlineStr">
         <is>
-          <t>Zhejiang Jiecang Linear Motion Technology Co.,Ltd</t>
+          <t>ZIMI INNOVATIONS PTY LTD</t>
         </is>
       </c>
       <c r="C459" s="5" t="inlineStr">
         <is>
-          <t>Matter 1.3 Window covering</t>
+          <t>Senoa Matter Power Point</t>
         </is>
       </c>
       <c r="D459" s="4" t="inlineStr">
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E459" s="4" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F459" s="4" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Smart plug</t>
         </is>
       </c>
       <c r="G459" s="5" t="inlineStr"/>
@@ -15195,12 +15195,12 @@
       </c>
       <c r="B460" s="7" t="inlineStr">
         <is>
-          <t>Zhejiang Moorgen Group Co., Ltd.</t>
+          <t>ZIMI INNOVATIONS PTY LTD</t>
         </is>
       </c>
       <c r="C460" s="7" t="inlineStr">
         <is>
-          <t>Crystal Series Rechargeable Lamp</t>
+          <t>Senoa Matter Switch</t>
         </is>
       </c>
       <c r="D460" s="6" t="inlineStr">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="F460" s="6" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G460" s="7" t="inlineStr"/>
@@ -15226,12 +15226,12 @@
       </c>
       <c r="B461" s="5" t="inlineStr">
         <is>
-          <t>Zhongshan Leshi IoT Technology Co.,LTD</t>
+          <t>Zemismart Technology Limited</t>
         </is>
       </c>
       <c r="C461" s="5" t="inlineStr">
         <is>
-          <t>Le Light 15T</t>
+          <t>Zemismart Lighting Kit</t>
         </is>
       </c>
       <c r="D461" s="4" t="inlineStr">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="F461" s="4" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Lightstrip</t>
         </is>
       </c>
       <c r="G461" s="5" t="inlineStr"/>
@@ -15257,12 +15257,12 @@
       </c>
       <c r="B462" s="7" t="inlineStr">
         <is>
-          <t>Zhuhai Ltech Technology Co., Ltd</t>
+          <t>Zemismart Technology Limited</t>
         </is>
       </c>
       <c r="C462" s="7" t="inlineStr">
         <is>
-          <t>Ltech Constant Current LED Driver (LA series)</t>
+          <t>Zemismart MT01 Slide Curtain</t>
         </is>
       </c>
       <c r="D462" s="6" t="inlineStr">
@@ -15272,12 +15272,12 @@
       </c>
       <c r="E462" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="F462" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Curtain</t>
         </is>
       </c>
       <c r="G462" s="7" t="inlineStr"/>
@@ -15288,12 +15288,12 @@
       </c>
       <c r="B463" s="5" t="inlineStr">
         <is>
-          <t>Zhuhai Ltech Technology Co., Ltd</t>
+          <t>Zemismart Technology Limited</t>
         </is>
       </c>
       <c r="C463" s="5" t="inlineStr">
         <is>
-          <t>Ltech Constant Current LED Driver (SE series)</t>
+          <t>Zemismart Motion Detector</t>
         </is>
       </c>
       <c r="D463" s="4" t="inlineStr">
@@ -15303,12 +15303,12 @@
       </c>
       <c r="E463" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="F463" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="G463" s="5" t="inlineStr"/>
@@ -15319,12 +15319,12 @@
       </c>
       <c r="B464" s="7" t="inlineStr">
         <is>
-          <t>Zhuhai Ltech Technology Co., Ltd</t>
+          <t>Zemismart Technology Limited</t>
         </is>
       </c>
       <c r="C464" s="7" t="inlineStr">
         <is>
-          <t>Ltech Constant Voltage LED Driver (LM, LA, HMA series)</t>
+          <t>Zemismart Thread Curtain Motor</t>
         </is>
       </c>
       <c r="D464" s="6" t="inlineStr">
@@ -15334,12 +15334,12 @@
       </c>
       <c r="E464" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F464" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Curtain</t>
         </is>
       </c>
       <c r="G464" s="7" t="inlineStr"/>
@@ -15350,12 +15350,12 @@
       </c>
       <c r="B465" s="5" t="inlineStr">
         <is>
-          <t>Zhuhai Ltech Technology Co., Ltd</t>
+          <t>Zemismart Technology Limited</t>
         </is>
       </c>
       <c r="C465" s="5" t="inlineStr">
         <is>
-          <t>Ltech Constant Voltage LED Driver (MA series)</t>
+          <t>Zemismart Window Shading System Driver</t>
         </is>
       </c>
       <c r="D465" s="4" t="inlineStr">
@@ -15365,12 +15365,12 @@
       </c>
       <c r="E465" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F465" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Curtain</t>
         </is>
       </c>
       <c r="G465" s="5" t="inlineStr"/>
@@ -15381,12 +15381,12 @@
       </c>
       <c r="B466" s="7" t="inlineStr">
         <is>
-          <t>Zhuhai Ltech Technology Co., Ltd</t>
+          <t>Zhejiang General light Curtain Co., Ltd.</t>
         </is>
       </c>
       <c r="C466" s="7" t="inlineStr">
         <is>
-          <t>Ltech Light Converter (E6, CG, KM families)</t>
+          <t>25 DC roller shutter motor</t>
         </is>
       </c>
       <c r="D466" s="6" t="inlineStr">
@@ -15396,12 +15396,12 @@
       </c>
       <c r="E466" s="6" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F466" s="6" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G466" s="7" t="inlineStr"/>
@@ -15412,12 +15412,12 @@
       </c>
       <c r="B467" s="5" t="inlineStr">
         <is>
-          <t>Zhuhai Ltech Technology Co., Ltd</t>
+          <t>Zhejiang Jiecang Linear Motion Technology Co.,Ltd</t>
         </is>
       </c>
       <c r="C467" s="5" t="inlineStr">
         <is>
-          <t>Ltech On/Off Light Driver</t>
+          <t>Matter 1.3 Window covering</t>
         </is>
       </c>
       <c r="D467" s="4" t="inlineStr">
@@ -15427,12 +15427,12 @@
       </c>
       <c r="E467" s="4" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="F467" s="4" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="G467" s="5" t="inlineStr"/>
@@ -15443,12 +15443,12 @@
       </c>
       <c r="B468" s="7" t="inlineStr">
         <is>
-          <t>Zumtobel Group AG</t>
+          <t>Zhejiang Moorgen Group Co., Ltd.</t>
         </is>
       </c>
       <c r="C468" s="7" t="inlineStr">
         <is>
-          <t>Driver LC 100W 24V MTR SC PRE2</t>
+          <t>Crystal Series Rechargeable Lamp</t>
         </is>
       </c>
       <c r="D468" s="6" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="F468" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G468" s="7" t="inlineStr"/>
@@ -15474,12 +15474,12 @@
       </c>
       <c r="B469" s="5" t="inlineStr">
         <is>
-          <t>Zumtobel Group AG</t>
+          <t>Zhongshan Leshi IoT Technology Co.,LTD</t>
         </is>
       </c>
       <c r="C469" s="5" t="inlineStr">
         <is>
-          <t>Driver LC 150W 24V MTR SC PRE2</t>
+          <t>Le Light 15T</t>
         </is>
       </c>
       <c r="D469" s="4" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="F469" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="G469" s="5" t="inlineStr"/>
@@ -15505,12 +15505,12 @@
       </c>
       <c r="B470" s="7" t="inlineStr">
         <is>
-          <t>Zumtobel Group AG</t>
+          <t>Zhuhai Ltech Technology Co., Ltd</t>
         </is>
       </c>
       <c r="C470" s="7" t="inlineStr">
         <is>
-          <t>Driver LC 35W 24V MTR SC PRE2</t>
+          <t>Ltech Constant Current LED Driver (LA series)</t>
         </is>
       </c>
       <c r="D470" s="6" t="inlineStr">
@@ -15536,12 +15536,12 @@
       </c>
       <c r="B471" s="5" t="inlineStr">
         <is>
-          <t>Zumtobel Group AG</t>
+          <t>Zhuhai Ltech Technology Co., Ltd</t>
         </is>
       </c>
       <c r="C471" s="5" t="inlineStr">
         <is>
-          <t>Driver LC 60W 24V MTR SC PRE2</t>
+          <t>Ltech Constant Current LED Driver (SE series)</t>
         </is>
       </c>
       <c r="D471" s="4" t="inlineStr">
@@ -15567,12 +15567,12 @@
       </c>
       <c r="B472" s="7" t="inlineStr">
         <is>
-          <t>Zumtobel Group AG</t>
+          <t>Zhuhai Ltech Technology Co., Ltd</t>
         </is>
       </c>
       <c r="C472" s="7" t="inlineStr">
         <is>
-          <t>Wireless Module MTR</t>
+          <t>Ltech Constant Voltage LED Driver (LM, LA, HMA series)</t>
         </is>
       </c>
       <c r="D472" s="6" t="inlineStr">
@@ -15598,12 +15598,12 @@
       </c>
       <c r="B473" s="5" t="inlineStr">
         <is>
-          <t>Zumtobel Group AG</t>
+          <t>Zhuhai Ltech Technology Co., Ltd</t>
         </is>
       </c>
       <c r="C473" s="5" t="inlineStr">
         <is>
-          <t>Wireless Module SR MTR</t>
+          <t>Ltech Constant Voltage LED Driver (MA series)</t>
         </is>
       </c>
       <c r="D473" s="4" t="inlineStr">
@@ -15629,12 +15629,12 @@
       </c>
       <c r="B474" s="7" t="inlineStr">
         <is>
-          <t>Zumtobel Group AG</t>
+          <t>Zhuhai Ltech Technology Co., Ltd</t>
         </is>
       </c>
       <c r="C474" s="7" t="inlineStr">
         <is>
-          <t>Wireless module passive MTR</t>
+          <t>Ltech Light Converter (E6, CG, KM families)</t>
         </is>
       </c>
       <c r="D474" s="6" t="inlineStr">
@@ -15660,27 +15660,27 @@
       </c>
       <c r="B475" s="5" t="inlineStr">
         <is>
-          <t>synaptics</t>
+          <t>Zhuhai Ltech Technology Co., Ltd</t>
         </is>
       </c>
       <c r="C475" s="5" t="inlineStr">
         <is>
-          <t>SYN4384 (as Thread RCP) + [Synaptics Linux host base on Raspberry Pi 4] Border Router</t>
+          <t>Ltech On/Off Light Driver</t>
         </is>
       </c>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E475" s="4" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F475" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G475" s="5" t="inlineStr"/>
@@ -15691,22 +15691,22 @@
       </c>
       <c r="B476" s="7" t="inlineStr">
         <is>
-          <t>synaptics</t>
+          <t>Zumtobel Group AG</t>
         </is>
       </c>
       <c r="C476" s="7" t="inlineStr">
         <is>
-          <t>Synaptics V1.3 Border Router Assembly - SYN20708 (as Thread RCP) + Linux Host</t>
+          <t>Driver LC 100W 24V MTR SC PRE2</t>
         </is>
       </c>
       <c r="D476" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E476" s="6" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F476" s="6" t="inlineStr">
@@ -15722,22 +15722,22 @@
       </c>
       <c r="B477" s="5" t="inlineStr">
         <is>
-          <t>synaptics</t>
+          <t>Zumtobel Group AG</t>
         </is>
       </c>
       <c r="C477" s="5" t="inlineStr">
         <is>
-          <t>Synaptics V1.4 Border Router Assembly - SYN20708 (as Thread RCP) + Raspberry Pi Linux host</t>
+          <t>Driver LC 150W 24V MTR SC PRE2</t>
         </is>
       </c>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E477" s="4" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F477" s="4" t="inlineStr">
@@ -15753,27 +15753,27 @@
       </c>
       <c r="B478" s="7" t="inlineStr">
         <is>
-          <t>tado</t>
+          <t>Zumtobel Group AG</t>
         </is>
       </c>
       <c r="C478" s="7" t="inlineStr">
         <is>
-          <t>Heat Pump Optimizer</t>
+          <t>Driver LC 35W 24V MTR SC PRE2</t>
         </is>
       </c>
       <c r="D478" s="6" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E478" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F478" s="6" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G478" s="7" t="inlineStr"/>
@@ -15784,22 +15784,22 @@
       </c>
       <c r="B479" s="5" t="inlineStr">
         <is>
-          <t>tado</t>
+          <t>Zumtobel Group AG</t>
         </is>
       </c>
       <c r="C479" s="5" t="inlineStr">
         <is>
-          <t>Internet Bridge X</t>
+          <t>Driver LC 60W 24V MTR SC PRE2</t>
         </is>
       </c>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
       <c r="E479" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F479" s="4" t="inlineStr">
@@ -15815,12 +15815,12 @@
       </c>
       <c r="B480" s="7" t="inlineStr">
         <is>
-          <t>tado</t>
+          <t>Zumtobel Group AG</t>
         </is>
       </c>
       <c r="C480" s="7" t="inlineStr">
         <is>
-          <t>Smart Radiator Thermostat X</t>
+          <t>Wireless Module MTR</t>
         </is>
       </c>
       <c r="D480" s="6" t="inlineStr">
@@ -15830,12 +15830,12 @@
       </c>
       <c r="E480" s="6" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F480" s="6" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G480" s="7" t="inlineStr"/>
@@ -15846,12 +15846,12 @@
       </c>
       <c r="B481" s="5" t="inlineStr">
         <is>
-          <t>tado</t>
+          <t>Zumtobel Group AG</t>
         </is>
       </c>
       <c r="C481" s="5" t="inlineStr">
         <is>
-          <t>Smart Radiator Thermostat X</t>
+          <t>Wireless Module SR MTR</t>
         </is>
       </c>
       <c r="D481" s="4" t="inlineStr">
@@ -15861,12 +15861,12 @@
       </c>
       <c r="E481" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F481" s="4" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G481" s="5" t="inlineStr"/>
@@ -15877,12 +15877,12 @@
       </c>
       <c r="B482" s="7" t="inlineStr">
         <is>
-          <t>tado</t>
+          <t>Zumtobel Group AG</t>
         </is>
       </c>
       <c r="C482" s="7" t="inlineStr">
         <is>
-          <t>Smart Thermostat X</t>
+          <t>Wireless module passive MTR</t>
         </is>
       </c>
       <c r="D482" s="6" t="inlineStr">
@@ -15892,12 +15892,12 @@
       </c>
       <c r="E482" s="6" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="F482" s="6" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="G482" s="7" t="inlineStr"/>
@@ -15908,27 +15908,27 @@
       </c>
       <c r="B483" s="5" t="inlineStr">
         <is>
-          <t>tado</t>
+          <t>synaptics</t>
         </is>
       </c>
       <c r="C483" s="5" t="inlineStr">
         <is>
-          <t>Smart Thermostat X Gen 2</t>
+          <t>SYN4384 (as Thread RCP) + [Synaptics Linux host base on Raspberry Pi 4] Border Router</t>
         </is>
       </c>
       <c r="D483" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E483" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="F483" s="4" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G483" s="5" t="inlineStr"/>
@@ -15939,12 +15939,12 @@
       </c>
       <c r="B484" s="7" t="inlineStr">
         <is>
-          <t>tado</t>
+          <t>synaptics</t>
         </is>
       </c>
       <c r="C484" s="7" t="inlineStr">
         <is>
-          <t>Wireless Receiver X</t>
+          <t>Synaptics V1.3 Border Router Assembly - SYN20708 (as Thread RCP) + Linux Host</t>
         </is>
       </c>
       <c r="D484" s="6" t="inlineStr">
@@ -15954,12 +15954,12 @@
       </c>
       <c r="E484" s="6" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F484" s="6" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G484" s="7" t="inlineStr"/>
@@ -15970,12 +15970,12 @@
       </c>
       <c r="B485" s="5" t="inlineStr">
         <is>
-          <t>tado</t>
+          <t>synaptics</t>
         </is>
       </c>
       <c r="C485" s="5" t="inlineStr">
         <is>
-          <t>Wireless Receiver X - Programmer with Hot Water Control and OpenTherm</t>
+          <t>Synaptics V1.4 Border Router Assembly - SYN20708 (as Thread RCP) + Raspberry Pi Linux host</t>
         </is>
       </c>
       <c r="D485" s="4" t="inlineStr">
@@ -15985,12 +15985,12 @@
       </c>
       <c r="E485" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="F485" s="4" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G485" s="5" t="inlineStr"/>
@@ -16006,22 +16006,22 @@
       </c>
       <c r="C486" s="7" t="inlineStr">
         <is>
-          <t>Wireless Temperature Sensor X</t>
+          <t>Heat Pump Optimizer</t>
         </is>
       </c>
       <c r="D486" s="6" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E486" s="6" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F486" s="6" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Heating</t>
         </is>
       </c>
       <c r="G486" s="7" t="inlineStr"/>
@@ -16037,22 +16037,22 @@
       </c>
       <c r="C487" s="5" t="inlineStr">
         <is>
-          <t>Wireless Temperature Sensor X (SU04)</t>
+          <t>Internet Bridge X</t>
         </is>
       </c>
       <c r="D487" s="4" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
       <c r="E487" s="4" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F487" s="4" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G487" s="5" t="inlineStr"/>
@@ -16068,28 +16068,276 @@
       </c>
       <c r="C488" s="7" t="inlineStr">
         <is>
+          <t>Smart Radiator Thermostat X</t>
+        </is>
+      </c>
+      <c r="D488" s="6" t="inlineStr">
+        <is>
+          <t>Built on Thread</t>
+        </is>
+      </c>
+      <c r="E488" s="6" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="F488" s="6" t="inlineStr">
+        <is>
+          <t>Heating</t>
+        </is>
+      </c>
+      <c r="G488" s="7" t="inlineStr"/>
+    </row>
+    <row r="489" ht="18" customHeight="1">
+      <c r="A489" s="4" t="n">
+        <v>485</v>
+      </c>
+      <c r="B489" s="5" t="inlineStr">
+        <is>
+          <t>tado</t>
+        </is>
+      </c>
+      <c r="C489" s="5" t="inlineStr">
+        <is>
+          <t>Smart Radiator Thermostat X</t>
+        </is>
+      </c>
+      <c r="D489" s="4" t="inlineStr">
+        <is>
+          <t>Built on Thread</t>
+        </is>
+      </c>
+      <c r="E489" s="4" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="F489" s="4" t="inlineStr">
+        <is>
+          <t>Heating</t>
+        </is>
+      </c>
+      <c r="G489" s="5" t="inlineStr"/>
+    </row>
+    <row r="490" ht="18" customHeight="1">
+      <c r="A490" s="6" t="n">
+        <v>486</v>
+      </c>
+      <c r="B490" s="7" t="inlineStr">
+        <is>
+          <t>tado</t>
+        </is>
+      </c>
+      <c r="C490" s="7" t="inlineStr">
+        <is>
+          <t>Smart Thermostat X</t>
+        </is>
+      </c>
+      <c r="D490" s="6" t="inlineStr">
+        <is>
+          <t>Built on Thread</t>
+        </is>
+      </c>
+      <c r="E490" s="6" t="inlineStr">
+        <is>
+          <t>Automation control</t>
+        </is>
+      </c>
+      <c r="F490" s="6" t="inlineStr">
+        <is>
+          <t>Heating</t>
+        </is>
+      </c>
+      <c r="G490" s="7" t="inlineStr"/>
+    </row>
+    <row r="491" ht="18" customHeight="1">
+      <c r="A491" s="4" t="n">
+        <v>487</v>
+      </c>
+      <c r="B491" s="5" t="inlineStr">
+        <is>
+          <t>tado</t>
+        </is>
+      </c>
+      <c r="C491" s="5" t="inlineStr">
+        <is>
+          <t>Smart Thermostat X Gen 2</t>
+        </is>
+      </c>
+      <c r="D491" s="4" t="inlineStr">
+        <is>
+          <t>Built on Thread</t>
+        </is>
+      </c>
+      <c r="E491" s="4" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="F491" s="4" t="inlineStr">
+        <is>
+          <t>Heating</t>
+        </is>
+      </c>
+      <c r="G491" s="5" t="inlineStr"/>
+    </row>
+    <row r="492" ht="18" customHeight="1">
+      <c r="A492" s="6" t="n">
+        <v>488</v>
+      </c>
+      <c r="B492" s="7" t="inlineStr">
+        <is>
+          <t>tado</t>
+        </is>
+      </c>
+      <c r="C492" s="7" t="inlineStr">
+        <is>
+          <t>Wireless Receiver X</t>
+        </is>
+      </c>
+      <c r="D492" s="6" t="inlineStr">
+        <is>
+          <t>Thread Certified Component</t>
+        </is>
+      </c>
+      <c r="E492" s="6" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="F492" s="6" t="inlineStr">
+        <is>
+          <t>Heating</t>
+        </is>
+      </c>
+      <c r="G492" s="7" t="inlineStr"/>
+    </row>
+    <row r="493" ht="18" customHeight="1">
+      <c r="A493" s="4" t="n">
+        <v>489</v>
+      </c>
+      <c r="B493" s="5" t="inlineStr">
+        <is>
+          <t>tado</t>
+        </is>
+      </c>
+      <c r="C493" s="5" t="inlineStr">
+        <is>
+          <t>Wireless Receiver X - Programmer with Hot Water Control and OpenTherm</t>
+        </is>
+      </c>
+      <c r="D493" s="4" t="inlineStr">
+        <is>
+          <t>Thread Certified Component</t>
+        </is>
+      </c>
+      <c r="E493" s="4" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="F493" s="4" t="inlineStr">
+        <is>
+          <t>Heating</t>
+        </is>
+      </c>
+      <c r="G493" s="5" t="inlineStr"/>
+    </row>
+    <row r="494" ht="18" customHeight="1">
+      <c r="A494" s="6" t="n">
+        <v>490</v>
+      </c>
+      <c r="B494" s="7" t="inlineStr">
+        <is>
+          <t>tado</t>
+        </is>
+      </c>
+      <c r="C494" s="7" t="inlineStr">
+        <is>
+          <t>Wireless Temperature Sensor X</t>
+        </is>
+      </c>
+      <c r="D494" s="6" t="inlineStr">
+        <is>
+          <t>Built on Thread</t>
+        </is>
+      </c>
+      <c r="E494" s="6" t="inlineStr">
+        <is>
+          <t>Sensor</t>
+        </is>
+      </c>
+      <c r="F494" s="6" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="G494" s="7" t="inlineStr"/>
+    </row>
+    <row r="495" ht="18" customHeight="1">
+      <c r="A495" s="4" t="n">
+        <v>491</v>
+      </c>
+      <c r="B495" s="5" t="inlineStr">
+        <is>
+          <t>tado</t>
+        </is>
+      </c>
+      <c r="C495" s="5" t="inlineStr">
+        <is>
+          <t>Wireless Temperature Sensor X (SU04)</t>
+        </is>
+      </c>
+      <c r="D495" s="4" t="inlineStr">
+        <is>
+          <t>Built on Thread</t>
+        </is>
+      </c>
+      <c r="E495" s="4" t="inlineStr">
+        <is>
+          <t>Sensor</t>
+        </is>
+      </c>
+      <c r="F495" s="4" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="G495" s="5" t="inlineStr"/>
+    </row>
+    <row r="496" ht="18" customHeight="1">
+      <c r="A496" s="6" t="n">
+        <v>492</v>
+      </c>
+      <c r="B496" s="7" t="inlineStr">
+        <is>
+          <t>tado</t>
+        </is>
+      </c>
+      <c r="C496" s="7" t="inlineStr">
+        <is>
           <t>Wireless Temperature Sensor X Gen 2</t>
         </is>
       </c>
-      <c r="D488" s="6" t="inlineStr">
-        <is>
-          <t>Built on Thread</t>
-        </is>
-      </c>
-      <c r="E488" s="6" t="inlineStr">
+      <c r="D496" s="6" t="inlineStr">
+        <is>
+          <t>Built on Thread</t>
+        </is>
+      </c>
+      <c r="E496" s="6" t="inlineStr">
         <is>
           <t>Sensor</t>
         </is>
       </c>
-      <c r="F488" s="6" t="inlineStr">
+      <c r="F496" s="6" t="inlineStr">
         <is>
           <t>Temperature</t>
         </is>
       </c>
-      <c r="G488" s="7" t="inlineStr"/>
+      <c r="G496" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G488"/>
+  <autoFilter ref="A4:G496"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -16190,7 +16438,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Air, Bulb, Contact, Light, Presence, Smart plug, Switch, Temperature, Water</t>
+          <t>Air, Bulb, Contact, Light, Presence, Smart plug, Switch, Water</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -16402,7 +16650,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>tado</t>
+          <t>What's Matter Inc.</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
@@ -16410,12 +16658,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Automation control, HVAC, Infrastructure, Sensor</t>
+          <t>Automation control, Sensor</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Heating, Temperature</t>
+          <t>Air, Contact, Light, Presence, Smoke alarm, Switch, Temperature, Water</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16427,32 +16675,32 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Dexatek Technology Ltd.,</t>
+          <t>tado</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Automation control, HVAC, Lighting, Sensor, Window covering</t>
+          <t>Automation control, HVAC, Infrastructure, Sensor</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Air conditioning, Blind, Contact, Curtain, Lighting, Shutter, Smart plug, Switch</t>
+          <t>Heating, Temperature</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Built on Thread, Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Espressif Systems (Shanghai) Co., Ltd.</t>
+          <t>Dexatek Technology Ltd.,</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
@@ -16460,24 +16708,24 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Automation control, Chipset, HVAC, Infrastructure, Lighting, Window covering</t>
+          <t>Automation control, HVAC, Lighting, Sensor, Window covering</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Heating, Hub, Smart plug, Switch</t>
+          <t>Air conditioning, Blind, Contact, Curtain, Lighting, Shutter, Smart plug, Switch</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Built on Thread, Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Qingdao Yeelink Information Technology Co., Ltd</t>
+          <t>Espressif Systems (Shanghai) Co., Ltd.</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
@@ -16485,12 +16733,12 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Automation control, HVAC, Infrastructure, Lighting</t>
+          <t>Automation control, Chipset, HVAC, Infrastructure, Lighting, Window covering</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Bulb, Hub, Light, Lightstrip, Switch</t>
+          <t>Heating, Hub, Smart plug, Switch</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -16502,7 +16750,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Samsung SmartThings</t>
+          <t>Qingdao Yeelink Information Technology Co., Ltd</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
@@ -16510,49 +16758,49 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Automation control, Infrastructure</t>
+          <t>Automation control, HVAC, Infrastructure, Lighting</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Hub, Smart speaker</t>
+          <t>Bulb, Hub, Light, Lightstrip, Switch</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread, Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Samsung SmartThings</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Infrastructure, Sensor</t>
+          <t>Automation control, Infrastructure</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Hub, Smart speaker</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread, Thread Certified Component</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Silicon Laboratories, Inc.</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
@@ -16560,24 +16808,24 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Chipset, Module</t>
+          <t>Infrastructure, Sensor</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread, Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>What's Matter Inc.</t>
+          <t>Silicon Laboratories, Inc.</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
@@ -16585,17 +16833,17 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Chipset, Module</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Air, Contact, Light, Presence, Smoke alarm, Temperature</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread, Thread Certified Component</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
@@ -16827,7 +17075,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Shenzhen Heiman Technology Co., Ltd.</t>
+          <t>STMicroelectronics International N.V.</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
@@ -16835,24 +17083,24 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Automation control, Safety, Sensor</t>
+          <t>Chipset, Module</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Gas alarm, Smart plug, Smoke alarm, Temperature, Water</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>WAREMA Renkhoff SE</t>
+          <t>Shenzhen Heiman Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
@@ -16860,12 +17108,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Automation control, Window covering</t>
+          <t>Automation control, Safety, Sensor</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Blind, Shutter, Switch</t>
+          <t>Gas alarm, Smart plug, Smoke alarm, Temperature, Water</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16877,7 +17125,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Zemismart Technology Limited</t>
+          <t>WAREMA Renkhoff SE</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
@@ -16885,12 +17133,12 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Automation control, Lighting, Sensor, Window covering</t>
+          <t>Automation control, Window covering</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Curtain, Lightstrip, Presence</t>
+          <t>Blind, Shutter, Switch</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -16902,20 +17150,20 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Allegion/Schlage Lock Company LLC</t>
+          <t>Zemismart Technology Limited</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Automation control, Lighting, Sensor, Window covering</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Curtain, Lightstrip, Presence</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16927,7 +17175,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Cascoda Limited</t>
+          <t>Allegion/Schlage Lock Company LLC</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
@@ -16935,24 +17183,24 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Infrastructure, Module, Sensor</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread, Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Inovelli Labs Corporation</t>
+          <t>Cascoda Limited</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
@@ -16960,24 +17208,24 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>HVAC, Lighting</t>
+          <t>Infrastructure, Module, Sensor</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Air, Switch</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Built on Thread, Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Nordic Semiconductor ASA</t>
+          <t>Inovelli Labs Corporation</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
@@ -16985,24 +17233,24 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>HVAC, Lighting</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Air, Switch</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Qorvo Utrecht B.V.</t>
+          <t>Nordic Semiconductor ASA</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
@@ -17027,7 +17275,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Robert Bosch GmbH</t>
+          <t>Qorvo Utrecht B.V.</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
@@ -17035,24 +17283,24 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Automation control, HVAC, Sensor</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Contact, Heating, Presence, Smart plug</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>STMicroelectronics International N.V.</t>
+          <t>Robert Bosch GmbH</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
@@ -17060,17 +17308,17 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Chipset, Module</t>
+          <t>Automation control, HVAC, Sensor</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Contact, Heating, Presence, Smart plug</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
@@ -17352,7 +17600,7 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>PIN Genie Inc, DBA Lockly</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
@@ -17360,24 +17608,24 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Chipset, Module</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>Shenzhen Sonoff Technologies Co.,Ltd.</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
@@ -17385,24 +17633,24 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Chipset, Module</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Contact, Presence, Temperature</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Sleekpoint Innovations Company Limited</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
@@ -17410,12 +17658,12 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Automation control, HVAC, Safety</t>
+          <t>Automation control, Sensor</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Air, Door lock, Switch</t>
+          <t>Switch, Temperature</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -17427,7 +17675,7 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc.</t>
+          <t>Shenzhen Sonoff Technologies Co.,Ltd.</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
@@ -17435,24 +17683,24 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Contact, Presence, Temperature</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>synaptics</t>
+          <t>Sleekpoint Innovations Company Limited</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
@@ -17460,32 +17708,32 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Chipset, Module</t>
+          <t>Automation control, HVAC, Safety</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Air, Door lock, Switch</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Arduino S.r.l.</t>
+          <t>Texas Instruments Inc.</t>
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -17502,32 +17750,32 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>BOKE Drivers Co., Ltd</t>
+          <t>synaptics</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Chipset, Module</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>CAME S.p.A.</t>
+          <t>Arduino S.r.l.</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
@@ -17535,24 +17783,24 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>HVAC, Infrastructure</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Gateway, Heating</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread, Thread Certified Component</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Chengdu Meross Technology Co., Ltd</t>
+          <t>BOKE Drivers Co., Ltd</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
@@ -17560,12 +17808,12 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>HVAC, Sensor</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17577,7 +17825,7 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>DELTA DORE SA</t>
+          <t>CAME S.p.A.</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
@@ -17585,24 +17833,24 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>HVAC, Infrastructure</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Blind, Shutter</t>
+          <t>Gateway, Heating</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Built on Thread, Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>EGLO LEUCHTEN</t>
+          <t>Chengdu Meross Technology Co., Ltd</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
@@ -17610,12 +17858,12 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>HVAC, Sensor</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17627,7 +17875,7 @@
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Earda Technologies Co., Ltd</t>
+          <t>DELTA DORE SA</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
@@ -17635,24 +17883,24 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Blind, Shutter</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>ITIUS GmbH</t>
+          <t>EGLO LEUCHTEN</t>
         </is>
       </c>
       <c r="B64" s="4" t="n">
@@ -17665,7 +17913,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17677,7 +17925,7 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Infineon Technologies Americas Corp.</t>
+          <t>Earda Technologies Co., Ltd</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
@@ -17685,7 +17933,7 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Chipset, Module</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -17702,7 +17950,7 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Insta GmbH</t>
+          <t>ITIUS GmbH</t>
         </is>
       </c>
       <c r="B66" s="4" t="n">
@@ -17710,12 +17958,12 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Automation control, Lighting</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Bulb</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17727,7 +17975,7 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>LEEDARSON IoT Technology Inc</t>
+          <t>Infineon Technologies Americas Corp.</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
@@ -17735,24 +17983,24 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Automation control, Lighting</t>
+          <t>Chipset, Module</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Bulb, Smart plug</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>MEAN WELL ENTERPRISES CO., LTD.</t>
+          <t>Insta GmbH</t>
         </is>
       </c>
       <c r="B68" s="4" t="n">
@@ -17760,12 +18008,12 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Automation control, Lighting</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17777,7 +18025,7 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Microchip Technology Inc</t>
+          <t>LEEDARSON IoT Technology Inc</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
@@ -17785,24 +18033,24 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Automation control, Lighting</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bulb, Smart plug</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>PIN Genie Inc, DBA Lockly</t>
+          <t>MEAN WELL ENTERPRISES CO., LTD.</t>
         </is>
       </c>
       <c r="B70" s="4" t="n">
@@ -17810,12 +18058,12 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17827,7 +18075,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>SHENZHEN DEASINO TECHNOLOGY CO.,LTD</t>
+          <t>Microchip Technology Inc</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
@@ -17835,24 +18083,24 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Module, Safety</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread, Thread Certified Component</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>SIEGENIA-AUBI KG</t>
+          <t>SHENZHEN DEASINO TECHNOLOGY CO.,LTD</t>
         </is>
       </c>
       <c r="B72" s="4" t="n">
@@ -17860,24 +18108,24 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Safety, Sensor</t>
+          <t>Module, Safety</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Contact, Window lock</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Built on Thread, Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Sercomm Corporation</t>
+          <t>SIEGENIA-AUBI KG</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
@@ -17885,24 +18133,24 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Safety, Sensor</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Wi-Fi Access Point</t>
+          <t>Contact, Window lock</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Shanghai Poyu Intelligent Technology Co., Ltd.</t>
+          <t>Sercomm Corporation</t>
         </is>
       </c>
       <c r="B74" s="4" t="n">
@@ -17910,12 +18158,12 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Wi-Fi Access Point</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17927,7 +18175,7 @@
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Shenzhen Haojai Lianchuang Technology Co.,Ltd</t>
+          <t>Shanghai Poyu Intelligent Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="B75" s="6" t="n">
@@ -17935,24 +18183,24 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Automation control, Window covering</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Blind, Switch</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Shenzhen Sunricher Technology Co.,Ltd.</t>
+          <t>Shenzhen Haojai Lianchuang Technology Co.,Ltd</t>
         </is>
       </c>
       <c r="B76" s="4" t="n">
@@ -17960,12 +18208,12 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Lighting, Sensor</t>
+          <t>Automation control, Window covering</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Contact, Switch</t>
+          <t>Blind, Switch</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17977,7 +18225,7 @@
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Sichuan Changhong Neonet Technologies Co.,Ltd.</t>
+          <t>Shenzhen Sunricher Technology Co.,Ltd.</t>
         </is>
       </c>
       <c r="B77" s="6" t="n">
@@ -17985,12 +18233,12 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Lighting, Sensor</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Contact, Water</t>
+          <t>Contact, Switch</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -18002,7 +18250,7 @@
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Skylux NV</t>
+          <t>Sichuan Changhong Neonet Technologies Co.,Ltd.</t>
         </is>
       </c>
       <c r="B78" s="4" t="n">
@@ -18010,12 +18258,12 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Contact, Water</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -18027,7 +18275,7 @@
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>ThirdReality, Inc.</t>
+          <t>Skylux NV</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
@@ -18035,12 +18283,12 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Light, Switch</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
@@ -18052,7 +18300,7 @@
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>ZIMI INNOVATIONS PTY LTD</t>
+          <t>ThirdReality, Inc.</t>
         </is>
       </c>
       <c r="B80" s="4" t="n">
@@ -18060,12 +18308,12 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Automation control, Lighting</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Smart plug, Switch</t>
+          <t>Light, Switch</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -18077,20 +18325,20 @@
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>A solution Co., Ltd.</t>
+          <t>ZIMI INNOVATIONS PTY LTD</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Automation control, Lighting</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Smart plug, Switch</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -18102,7 +18350,7 @@
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>AC lnfinity</t>
+          <t>A solution Co., Ltd.</t>
         </is>
       </c>
       <c r="B82" s="4" t="n">
@@ -18110,12 +18358,12 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Air conditioning</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -18127,7 +18375,7 @@
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>ALRE IT Regeltechnik GmbH</t>
+          <t>AC lnfinity</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
@@ -18140,7 +18388,7 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Air conditioning</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -18152,7 +18400,7 @@
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Aeotec Group GmbH</t>
+          <t>ALRE IT Regeltechnik GmbH</t>
         </is>
       </c>
       <c r="B84" s="4" t="n">
@@ -18160,24 +18408,24 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Albrecht Jung GmbH &amp; Co. KG</t>
+          <t>Aeotec Group GmbH</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
@@ -18185,24 +18433,24 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Arpobot Pty Ltd</t>
+          <t>Albrecht Jung GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="B86" s="4" t="n">
@@ -18210,12 +18458,12 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -18227,7 +18475,7 @@
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Askey Computer Corp.</t>
+          <t>Arpobot Pty Ltd</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
@@ -18235,24 +18483,24 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Wi-Fi Access Point</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Assa Abloy</t>
+          <t>Askey Computer Corp.</t>
         </is>
       </c>
       <c r="B88" s="4" t="n">
@@ -18260,24 +18508,24 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Wi-Fi Access Point</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Athom B.V.</t>
+          <t>Assa Abloy</t>
         </is>
       </c>
       <c r="B89" s="6" t="n">
@@ -18285,24 +18533,24 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Atouch Winwel Lda</t>
+          <t>Athom B.V.</t>
         </is>
       </c>
       <c r="B90" s="4" t="n">
@@ -18310,24 +18558,24 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Beken Corporation</t>
+          <t>Atouch Winwel Lda</t>
         </is>
       </c>
       <c r="B91" s="6" t="n">
@@ -18335,24 +18583,24 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Bold Security Technology B.V.</t>
+          <t>Beken Corporation</t>
         </is>
       </c>
       <c r="B92" s="4" t="n">
@@ -18360,24 +18608,24 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>Bouygues Telecom</t>
+          <t>Bold Security Technology B.V.</t>
         </is>
       </c>
       <c r="B93" s="6" t="n">
@@ -18385,12 +18633,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Media streamer</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
@@ -18402,7 +18650,7 @@
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Changsha Xizhen Electronics Technology Co., Ltd.</t>
+          <t>Bouygues Telecom</t>
         </is>
       </c>
       <c r="B94" s="4" t="n">
@@ -18410,12 +18658,12 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Presence</t>
+          <t>Media streamer</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -18427,7 +18675,7 @@
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Changzhou Yooksmart Innovation Co.,Ltd</t>
+          <t>Changsha Xizhen Electronics Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="B95" s="6" t="n">
@@ -18435,12 +18683,12 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Presence</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -18452,7 +18700,7 @@
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>D-Link Corporation</t>
+          <t>Changzhou Yooksmart Innovation Co.,Ltd</t>
         </is>
       </c>
       <c r="B96" s="4" t="n">
@@ -18460,24 +18708,24 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Gateway</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Dendo Systems Pty Ltd</t>
+          <t>D-Link Corporation</t>
         </is>
       </c>
       <c r="B97" s="6" t="n">
@@ -18485,24 +18733,24 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>EMmicroelectronic</t>
+          <t>Dendo Systems Pty Ltd</t>
         </is>
       </c>
       <c r="B98" s="4" t="n">
@@ -18510,24 +18758,24 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>Ellard</t>
+          <t>EMmicroelectronic</t>
         </is>
       </c>
       <c r="B99" s="6" t="n">
@@ -18535,24 +18783,24 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Enlight International Ltd.</t>
+          <t>Ellard</t>
         </is>
       </c>
       <c r="B100" s="4" t="n">
@@ -18560,12 +18808,12 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -18577,7 +18825,7 @@
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>Fortune Brands Innovations, Inc.</t>
+          <t>Enlight International Ltd.</t>
         </is>
       </c>
       <c r="B101" s="6" t="n">
@@ -18585,12 +18833,12 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -18602,7 +18850,7 @@
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Grimsholm Products AB</t>
+          <t>Fortune Brands Innovations, Inc.</t>
         </is>
       </c>
       <c r="B102" s="4" t="n">
@@ -18610,12 +18858,12 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Irrigation</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -18627,7 +18875,7 @@
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>Guangzhou Skydance Co., Ltd</t>
+          <t>Grimsholm Products AB</t>
         </is>
       </c>
       <c r="B103" s="6" t="n">
@@ -18635,12 +18883,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Automation control</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Irrigation</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -18652,7 +18900,7 @@
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>HUZHOU DOORMA INTEL TECH CO LTD</t>
+          <t>Guangzhou Skydance Co., Ltd</t>
         </is>
       </c>
       <c r="B104" s="4" t="n">
@@ -18660,12 +18908,12 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -18677,7 +18925,7 @@
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>Hangzhou Ezviz Network Co., Ltd</t>
+          <t>HUZHOU DOORMA INTEL TECH CO LTD</t>
         </is>
       </c>
       <c r="B105" s="6" t="n">
@@ -18685,12 +18933,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Curtain</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
@@ -18702,7 +18950,7 @@
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Hangzhou Wistar Mechanical &amp; Electric Technology Co., Ltd</t>
+          <t>Hangzhou Ezviz Network Co., Ltd</t>
         </is>
       </c>
       <c r="B106" s="4" t="n">
@@ -18710,12 +18958,12 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -18727,7 +18975,7 @@
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>Hinkley Lighting Inc.</t>
+          <t>Hangzhou Wistar Mechanical &amp; Electric Technology Co., Ltd</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
@@ -18735,12 +18983,12 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
@@ -18752,7 +19000,7 @@
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>LOCKIN (U.S.) INC.</t>
+          <t>Hinkley Lighting Inc.</t>
         </is>
       </c>
       <c r="B108" s="4" t="n">
@@ -18760,12 +19008,12 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -18777,7 +19025,7 @@
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>LOCKIN (U.S.) INC.</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
@@ -18785,12 +19033,12 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
@@ -18802,7 +19050,7 @@
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Level Home Inc.</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="B110" s="4" t="n">
@@ -18810,12 +19058,12 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -18827,7 +19075,7 @@
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>MIWA LOCK Co., LTD.</t>
+          <t>Level Home Inc.</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
@@ -18852,7 +19100,7 @@
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>MMB Networks</t>
+          <t>MIWA LOCK Co., LTD.</t>
         </is>
       </c>
       <c r="B112" s="4" t="n">
@@ -18860,12 +19108,12 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -18877,7 +19125,7 @@
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>Mediola connected living AG</t>
+          <t>MMB Networks</t>
         </is>
       </c>
       <c r="B113" s="6" t="n">
@@ -18885,24 +19133,24 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Mighton Products Ltd</t>
+          <t>Mediola connected living AG</t>
         </is>
       </c>
       <c r="B114" s="4" t="n">
@@ -18910,24 +19158,24 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>Mikrotikls SIA</t>
+          <t>Mighton Products Ltd</t>
         </is>
       </c>
       <c r="B115" s="6" t="n">
@@ -18935,12 +19183,12 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Door lock</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -18952,7 +19200,7 @@
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Ningbo Dooya Mechanic &amp; Electronic Technology Co., Ltd</t>
+          <t>Mikrotikls SIA</t>
         </is>
       </c>
       <c r="B116" s="4" t="n">
@@ -18960,12 +19208,12 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Blind</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -18977,7 +19225,7 @@
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>ORANGE</t>
+          <t>Ningbo Dooya Mechanic &amp; Electronic Technology Co., Ltd</t>
         </is>
       </c>
       <c r="B117" s="6" t="n">
@@ -18985,24 +19233,24 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Wi-Fi Access Point</t>
+          <t>Blind</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>Thread Certified Component</t>
+          <t>Built on Thread</t>
         </is>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Qingdao Heffeix Technology Co., Ltd</t>
+          <t>ORANGE</t>
         </is>
       </c>
       <c r="B118" s="4" t="n">
@@ -19010,12 +19258,12 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Wi-Fi Access Point</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -19027,7 +19275,7 @@
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>Qualcomm Inc.</t>
+          <t>Qingdao Heffeix Technology Co., Ltd</t>
         </is>
       </c>
       <c r="B119" s="6" t="n">
@@ -19035,7 +19283,7 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>Chipset</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
@@ -19052,7 +19300,7 @@
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Quectel Wireless Solutions Co., Ltd.</t>
+          <t>Qualcomm Inc.</t>
         </is>
       </c>
       <c r="B120" s="4" t="n">
@@ -19060,7 +19308,7 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Chipset</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
@@ -19077,7 +19325,7 @@
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>SENSEREO LIMITED</t>
+          <t>Quectel Wireless Solutions Co., Ltd.</t>
         </is>
       </c>
       <c r="B121" s="6" t="n">
@@ -19085,24 +19333,24 @@
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Smoke alarm</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>Built on Thread</t>
+          <t>Thread Certified Component</t>
         </is>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Savant</t>
+          <t>SENSEREO LIMITED</t>
         </is>
       </c>
       <c r="B122" s="4" t="n">
@@ -19110,12 +19358,12 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Window covering</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>Smoke alarm</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -19127,7 +19375,7 @@
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Savant</t>
         </is>
       </c>
       <c r="B123" s="6" t="n">
@@ -19135,12 +19383,12 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>Automation control</t>
+          <t>Window covering</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Curtain</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
@@ -19628,7 +19876,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -19636,7 +19884,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -19700,7 +19948,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -19708,7 +19956,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -19718,7 +19966,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -19736,7 +19984,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -19744,7 +19992,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -19754,7 +20002,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -19820,7 +20068,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
@@ -19860,7 +20108,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -19900,7 +20148,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>337</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24">
@@ -19918,7 +20166,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25">
@@ -19972,7 +20220,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
@@ -20008,7 +20256,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -20068,7 +20316,7 @@
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>tado</t>
+          <t>What's Matter Inc.</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -20078,17 +20326,17 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dexatek Technology Ltd.,</t>
+          <t>tado</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>Espressif Systems (Shanghai) Co., Ltd.</t>
+          <t>Dexatek Technology Ltd.,</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -20098,7 +20346,7 @@
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>Qingdao Yeelink Information Technology C</t>
+          <t>Espressif Systems (Shanghai) Co., Ltd.</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -20108,7 +20356,7 @@
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>Samsung SmartThings</t>
+          <t>Qingdao Yeelink Information Technology C</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -20118,17 +20366,17 @@
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Samsung SmartThings</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>Silicon Laboratories, Inc.</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -20138,7 +20386,7 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>What's Matter Inc.</t>
+          <t>Silicon Laboratories, Inc.</t>
         </is>
       </c>
       <c r="C40" t="n">
